--- a/docs/xlsx/jobs-2026-10-27.xlsx
+++ b/docs/xlsx/jobs-2026-10-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="611">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,564 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Administrative Specialist</t>
+  </si>
+  <si>
+    <t>Kansas Department of Wildlife and Parks</t>
+  </si>
+  <si>
+    <t>Pratt, KS</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$18.44 - $19.36 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-administrative-specialist-pratt-kansas/8502561216</t>
+  </si>
+  <si>
+    <t>Associate Director of Brand &amp; Digital Strategy</t>
+  </si>
+  <si>
+    <t>Western Resource Advocates (WRA)</t>
+  </si>
+  <si>
+    <t>Santa Fe, NM</t>
+  </si>
+  <si>
+    <t>$97,750 - $115,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-associate-director-of-brand--digital-strategy-santa-fe-new-mexico/9260579080</t>
+  </si>
+  <si>
+    <t>Digital Engagement Specialist</t>
+  </si>
+  <si>
+    <t>$62,458 - $73,480 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-digital-engagement-specialist-santa-fe-new-mexico/4665519417</t>
+  </si>
+  <si>
+    <t>eeCorps Education Programs Assistant - Dinosaur Ridge</t>
+  </si>
+  <si>
+    <t>Colorado Alliance for Environmental Education</t>
+  </si>
+  <si>
+    <t>Morrison, CO</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$1,833.34 per month</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-eecorps-education-programs-assistant---dinosaur-ridge-morrison-colorado/9435763530</t>
+  </si>
+  <si>
+    <t>eeCorps Environmental Educator - Bird Conservancy of the Rockies</t>
+  </si>
+  <si>
+    <t>Brighton, CO</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-eecorps-environmental-educator---bird-conservancy-of-the-rockies-brighton-colorado/9136741626</t>
+  </si>
+  <si>
+    <t>eeCorps Environmental Educator - Denver Audubon</t>
+  </si>
+  <si>
+    <t>Littleton, CO</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-eecorps-environmental-educator---denver-audubon-littleton-colorado/9112186970</t>
+  </si>
+  <si>
+    <t>eeCorps NCA Environmental Educator - Colorado Canyons Association</t>
+  </si>
+  <si>
+    <t>Grand Junction, CO</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-eecorps-nca-environmental-educator---colorado-canyons-association-grand-junction-colorado/7551699601</t>
+  </si>
+  <si>
+    <t>eeCorps Summer Camp Assistant Director - Bluff Lake Nature Center</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation-admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-eecorps-summer-camp-assistant-director---bluff-lake-nature-center-denver-colorado/8643521504</t>
+  </si>
+  <si>
+    <t>Environmental Education Internship</t>
+  </si>
+  <si>
+    <t>Fossil Rim Wildlife Center</t>
+  </si>
+  <si>
+    <t>Glen Rose, TX</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$400 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-education-internship-glen-rose-texas/5365558444</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Sustainable Saratoga</t>
+  </si>
+  <si>
+    <t>Saratoga Springs, NY</t>
+  </si>
+  <si>
+    <t>$65,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-saratoga-springs-new-york/6306825764</t>
+  </si>
+  <si>
+    <t>Finance &amp; Accounting Manager</t>
+  </si>
+  <si>
+    <t>Nantucket Conservation Foundation</t>
+  </si>
+  <si>
+    <t>Nantucket, MA</t>
+  </si>
+  <si>
+    <t>$90,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>Green Jobs, Idealist</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-finance--accounting-manager-nantucket-massachusetts/7136988232</t>
+  </si>
+  <si>
+    <t>Grassroots Mobilization and Communications Manager</t>
+  </si>
+  <si>
+    <t>Standing Trees</t>
+  </si>
+  <si>
+    <t>Montpelier, VT</t>
+  </si>
+  <si>
+    <t>$45,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-grassroots-mobilization-and-communications-manager-montpelier-vermont/2969954811</t>
+  </si>
+  <si>
+    <t>Natural Resources Specialist</t>
+  </si>
+  <si>
+    <t>Center for Environmental Management Military Lands</t>
+  </si>
+  <si>
+    <t>Cheyenne, WY</t>
+  </si>
+  <si>
+    <t>$73,000 - $93,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-specialist-cheyenne-wyoming/7979399156</t>
+  </si>
+  <si>
+    <t>Outdoor Education Instructor</t>
+  </si>
+  <si>
+    <t>Pali Institute</t>
+  </si>
+  <si>
+    <t>Running Springs, CA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>Total Compensation Package from $1030-$1075 a week</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outdoor-education-instructor-running-springs-california/3776022738</t>
+  </si>
+  <si>
+    <t>Resource Protection Manager</t>
+  </si>
+  <si>
+    <t>Panthera</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>Competitive Salary and benefits</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-resource-protection-manager-new-york-new-york/9072528161</t>
+  </si>
+  <si>
+    <t>Senior Coral Production and Aquaculture Manager</t>
+  </si>
+  <si>
+    <t>Reef Renewal USA</t>
+  </si>
+  <si>
+    <t>Ruskin, FL</t>
+  </si>
+  <si>
+    <t>$75,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>fisheries-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-coral-production-and-aquaculture-manager-ruskin-florida/5175708401</t>
+  </si>
+  <si>
+    <t>Site Manager</t>
+  </si>
+  <si>
+    <t>Prairie Restorations Inc.</t>
+  </si>
+  <si>
+    <t>Randolph, MN</t>
+  </si>
+  <si>
+    <t>$57,510 - $72,420 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-site-manager-randolph-minnesota/1813547671</t>
+  </si>
+  <si>
+    <t>Stewardship Coordinator</t>
+  </si>
+  <si>
+    <t>The Land Trust for Tennessee</t>
+  </si>
+  <si>
+    <t>Chattanooga, TN</t>
+  </si>
+  <si>
+    <t>Starting at $48,000, dependent on experience</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stewardship-coordinator-chattanooga-tennessee/5736329102</t>
+  </si>
+  <si>
+    <t>USDA-FS Fellowship for Preparation and Analysis of Environmental Samples for Forest Productivity Studies</t>
+  </si>
+  <si>
+    <t>U.S. Department of Agriculture (USDA)</t>
+  </si>
+  <si>
+    <t>Grand Rapids, MN</t>
+  </si>
+  <si>
+    <t>Stipend $680.00 – $1,360.00 Monthly</t>
+  </si>
+  <si>
+    <t>ecology-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-fs-fellowship-for-preparation-and-analysis-of-environmental-samples-for-forest-productivity-studies-grand-rapids-minnesota/4526570270</t>
+  </si>
+  <si>
+    <t>USDA-FS Tracking Changes in Soil Frost and Implications for Forest Operations</t>
+  </si>
+  <si>
+    <t>Stipend $1,750.00 – $2,000.00 Monthly</t>
+  </si>
+  <si>
+    <t>ecology-forestry-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-fs-tracking-changes-in-soil-frost-and-implications-for-forest-operations-grand-rapids-minnesota/5996589569</t>
+  </si>
+  <si>
+    <t>Uwharrie Prescribed Fire/Fuels Module Lead</t>
+  </si>
+  <si>
+    <t>The Ember Alliance</t>
+  </si>
+  <si>
+    <t>Troy, NC</t>
+  </si>
+  <si>
+    <t>$26 per hour</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-uwharrie-prescribed-firefuels-module-lead-troy-north-carolina/3794339782</t>
+  </si>
+  <si>
+    <t>Wildlife Technician</t>
+  </si>
+  <si>
+    <t>UrbanX Pest &amp; Wildlife Removal Service</t>
+  </si>
+  <si>
+    <t>Belleville, NJ</t>
+  </si>
+  <si>
+    <t>$30,000 - $50,000 per year</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-technician-belleville-new-jersey/3978618163</t>
+  </si>
+  <si>
+    <t>Nantucket, Massachusetts, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Finance / Investing</t>
+  </si>
+  <si>
+    <t>Conservation Job Board, Idealist</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/finance-accounting-manager/</t>
+  </si>
+  <si>
+    <t>ACT Now Policy and Communications Fellow</t>
+  </si>
+  <si>
+    <t>Afterschool for Children and Teens Now (ACT Now)</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/92e2a1b8fac440229a5fb19691cbe8fc-act-now-policy-and-communications-fellow-afterschool-for-children-and-teens-now-act-now-chicago</t>
+  </si>
+  <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>De Novo Center For Justice and Healing</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/388e1835a57947d59fdc73d44c2dd419-administrative-assistant-de-novo-center-for-justice-and-healing-cambridge</t>
+  </si>
+  <si>
+    <t>Agente en vía pública | CABA y GBA</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles SOS Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d24d371ba556422bb653644287c705a7-agente-en-via-publica-caba-y-gba-aldeas-infantiles-sos-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General, Rochester Regional Office (3923)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>USD 87356.00 - 186494.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/05abda492bba4885b6334693189bd33c-assistant-attorney-general-rochester-regional-office-3923-new-york-state-office-of-the-attorney-general-rochester</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General, Syracuse Regional Office (3924)</t>
+  </si>
+  <si>
+    <t>Syracuse, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/1bb326e557dd4cf0a32acd3583c5100e-assistant-attorney-general-syracuse-regional-office-3924-new-york-state-office-of-the-attorney-general-syracuse</t>
+  </si>
+  <si>
+    <t>Associate Counsel</t>
+  </si>
+  <si>
+    <t>Whistleblower Aid</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4860fa5dba9a4abc9f1f4d67c5739c40-associate-counsel-whistleblower-aid-washington</t>
+  </si>
+  <si>
+    <t>Associate General Counsel for NYS Attorney General (3922)</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 91506.00 - 190644.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/c422276a02c941c89b689b3ce9cea0d0-associate-general-counsel-for-nys-attorney-general-3922-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Attorney: Investigate and Litigate Affirmative Cases (3921)</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 87594.00 - 186493.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/9b1de0f469c444cfb393bf4e1485e1f2-attorney-investigate-and-litigate-affirmative-cases-3921-new-york-state-office-of-the-attorney-general-albany</t>
+  </si>
+  <si>
+    <t>Attorney: Transactions Section, Charities Bureau (3920)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/af28a898fd4640b5a791929351aa9d05-attorney-transactions-section-charities-bureau-3920-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Billing Specialist</t>
+  </si>
+  <si>
+    <t>Springwell, Inc.</t>
+  </si>
+  <si>
+    <t>Waltham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61489ee558bd40ed96d53bd041b2effa-billing-specialist-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Business Manager - Part time: Finance and HR</t>
+  </si>
+  <si>
+    <t>San Miguel School Chicago</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9251d599c2744c3f876e04928cf2429f-business-manager-part-time-finance-and-hr-san-miguel-school-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Campaign Communications Organizer</t>
+  </si>
+  <si>
+    <t>Inquilinxs Unidxs Por Justicia</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 58275.00 - 58275.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6b433b60e41481ebb6a76c37dadba96-campaign-communications-organizer-inquilinxs-unidxs-por-justicia-minneapolis</t>
+  </si>
+  <si>
     <t>Caregiver</t>
   </si>
   <si>
@@ -49,9 +607,6 @@
     <t>Petaling Jaya, Selangor, MY</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>MYR 2090.00 - 2500.00/month</t>
   </si>
   <si>
@@ -61,16 +616,1237 @@
     <t>https://www.idealist.org/en/nonprofit-job/edbdb802c13e43a7b106ded7b37954d5-caregiver-shelter-home-for-children-petaling-jaya</t>
   </si>
   <si>
+    <t>Chief Development Officer</t>
+  </si>
+  <si>
+    <t>Family Promise</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 160000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9efaa886932843328e80da8cb15044a7-chief-development-officer-family-promise-summit</t>
+  </si>
+  <si>
     <t>Child Welfare Driver</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>MYR 1900.00/month</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/0cf644fc24ad4dfe8ddb361e13eb88b2-child-welfare-driver-shelter-home-for-children-petaling-jaya</t>
+  </si>
+  <si>
+    <t>College and Career Success, Program Manager (Years 3 &amp; 4)</t>
+  </si>
+  <si>
+    <t>Big Brothers Big Sisters of New York City</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b6e1d3e86204b7f90aefe61a1b94f4f-college-and-career-success-program-manager-years-3-4-big-brothers-big-sisters-of-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Communications and Outreach Associate</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>Remote (District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Lgbtq, Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8dca534f618141e2ab822e01ae951f6b-communications-and-outreach-associate-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Community Development Manager</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1c616041b42b425ea75b857054927c43-community-development-manager-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Community Justice Attorney, Immigrant Rights Program</t>
+  </si>
+  <si>
+    <t>AFSC (American Friends Service Committee)</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b3bcb84b4c8416085f522b6a2d9feed-community-justice-attorney-immigrant-rights-program-afsc-american-friends-service-committee-newark</t>
+  </si>
+  <si>
+    <t>Coordinator, Strategic Initiatives</t>
+  </si>
+  <si>
+    <t>Campus Compact</t>
+  </si>
+  <si>
+    <t>USD 59000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f38a4a72aef04a2ab43eb4c460b20cda-coordinator-strategic-initiatives-campus-compact-boston</t>
+  </si>
+  <si>
+    <t>Data and Billing Specialist</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/331941466ebf4123b4a857f53bdb8156-data-and-billing-specialist-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Development &amp; Events Associate</t>
+  </si>
+  <si>
+    <t>Massachusetts Law Reform Institute (MLRI)</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/708b6eb680d741ae9aff996a21577a9b-development-events-associate-massachusetts-law-reform-institute-mlri-boston</t>
+  </si>
+  <si>
+    <t>Development Associate (Part-Time) - Pet Partners (Bellevue, WA Headquarters - In Office)</t>
+  </si>
+  <si>
+    <t>Pet Partners</t>
+  </si>
+  <si>
+    <t>Bellevue, Washington</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Animals, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8eebdf3866fe416785ce95b7d088e5bb-development-associate-part-time-pet-partners-bellevue-wa-headquarters-in-office-pet-partners-bellevue</t>
+  </si>
+  <si>
+    <t>Digital Media and Communications Coordinator</t>
+  </si>
+  <si>
+    <t>Do Good Institute</t>
+  </si>
+  <si>
+    <t>College Park, Maryland</t>
+  </si>
+  <si>
+    <t>USD 69000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d5ebd4961bf45d7b80a4fa1e2ea31f5-digital-media-and-communications-coordinator-do-good-institute-college-park</t>
+  </si>
+  <si>
+    <t>Director of Charitable Planning</t>
+  </si>
+  <si>
+    <t>Community Foundation for Greater New Haven</t>
+  </si>
+  <si>
+    <t>New Haven, CT</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/efcfc958a1904bcd975578e5c90c8ae1-director-of-charitable-planning-community-foundation-for-greater-new-haven-new-haven</t>
+  </si>
+  <si>
+    <t>Director of Client Services</t>
+  </si>
+  <si>
+    <t>Patriot Paws Service Dogs</t>
+  </si>
+  <si>
+    <t>Rockwall, Texas</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e0c6dfd7736f45dc9af9558a82f91571-director-of-client-services-patriot-paws-service-dogs-rockwall</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Orphans of the Storm</t>
+  </si>
+  <si>
+    <t>Riverwoods, Illinois</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c3d83d3c5f74ac3a6adca7a92b98ef8-director-of-development-orphans-of-the-storm-riverwoods</t>
+  </si>
+  <si>
+    <t>Edu-Futuro</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ac79bfb591d45608ffd6484ea2a2816-director-of-development-edu-futuro-arlington</t>
+  </si>
+  <si>
+    <t>Moms First</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Media, Policy, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7acfda60aff4aa8a6937e2877238304-director-of-development-moms-first-new-york</t>
+  </si>
+  <si>
+    <t>Director of Development &amp; Communications</t>
+  </si>
+  <si>
+    <t>VertueLab</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 87000.00 - 91000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Philanthropy, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1a8c50890b743e0af7c9a7a8827980d-director-of-development-communications-vertuelab-portland</t>
+  </si>
+  <si>
+    <t>Director of People &amp; Operations</t>
+  </si>
+  <si>
+    <t>Meals On Wheels Chicago</t>
+  </si>
+  <si>
+    <t>Disability, Poverty, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9290836d8ff24918ba02c2bd661aa3ec-director-of-people-operations-meals-on-wheels-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Director, Clearinghouse Services</t>
+  </si>
+  <si>
+    <t>Health Resources in Action, Inc.</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e706217cf4c647eea560cec9b2a03b85-director-clearinghouse-services-health-resources-in-action-inc-boston</t>
+  </si>
+  <si>
+    <t>Ejecutivo Telefonico</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles SOS México, I. A. P</t>
+  </si>
+  <si>
+    <t>Ciudad de Mexico, Ciudad de Mexico, MX</t>
+  </si>
+  <si>
+    <t>MXN 10300.00 - 10500.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9efb14a0022f44148ccddc437b7d620c-ejecutivo-telefonico-aldeas-infantiles-sos-mexico-i-a-p-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Ejecutivo Telemarketing</t>
+  </si>
+  <si>
+    <t>Ciudad De México, Mexico, MX</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e275e549e554333adf677353b7a82c6-ejecutivo-telemarketing-aldeas-infantiles-sos-mexico-i-a-p-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>Voto Latino</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6c49e87c89640398649e9b6544428ae-executive-assistant-voto-latino-washington</t>
+  </si>
+  <si>
+    <t>Metropolitan Transportation Commission (MTC)</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 112139.72 - 142220.28/year</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/17288759dd9c412c92c251ec3da736d7-executive-assistant-metropolitan-transportation-commission-mtc-san-francisco</t>
+  </si>
+  <si>
+    <t>EngageWell IPA</t>
+  </si>
+  <si>
+    <t>Remote (New York, New York)</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a40b26c118b14b4a9fd4acbe83d3e3f8-executive-director-engagewell-ipa-new-york</t>
+  </si>
+  <si>
+    <t>National Education Association of New Mexico</t>
+  </si>
+  <si>
+    <t>Santa Fe, New Mexico</t>
+  </si>
+  <si>
+    <t>USD 126000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fcfe70ea9fe94c51b6f8d5b4d7ff9c3e-executive-director-national-education-association-of-new-mexico-santa-fe</t>
+  </si>
+  <si>
+    <t>SOLACE FRIENDS INC</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8de0f0e73f444db8b4b37e96ac05d7fc-executive-director-solace-friends-inc-madison</t>
+  </si>
+  <si>
+    <t>BloomAgainBklyn, Inc.</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d4a140a22ca0417cbfb954ea762baeae-executive-director-bloomagainbklyn-inc-kings-county</t>
+  </si>
+  <si>
+    <t>Aurora East Education Foundation</t>
+  </si>
+  <si>
+    <t>Aurora, Illinois</t>
+  </si>
+  <si>
+    <t>USD 40000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc36f6f481954c37b7b5a72351430308-executive-director-aurora-east-education-foundation-aurora</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Conservation Job Board, Green Jobs</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c2bfa46b1174a47937e9c93117403a3-finance-accounting-manager-nantucket-conservation-foundation-nantucket</t>
+  </si>
+  <si>
+    <t>Finance &amp; Budget Manager</t>
+  </si>
+  <si>
+    <t>Partners for Public Good</t>
+  </si>
+  <si>
+    <t>USD 113000.00 - 113000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f3fb9cea436b40f6819d17d30b3d9990-finance-budget-manager-partners-for-public-good-los-angeles</t>
+  </si>
+  <si>
+    <t>Finance and Operations Manager (Part-Time)</t>
+  </si>
+  <si>
+    <t>American Jesuits International</t>
+  </si>
+  <si>
+    <t>Community Development, Disaster Relief, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/18b2009a62324da490630165f317cf66-finance-and-operations-manager-part-time-american-jesuits-international-washington</t>
+  </si>
+  <si>
+    <t>Finance Assistant</t>
+  </si>
+  <si>
+    <t>Centro de Informacion</t>
+  </si>
+  <si>
+    <t>Elgin, Illinois</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 24.50/hour</t>
+  </si>
+  <si>
+    <t>Education, Hunger Food Security, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e07d902f83d4547802cecd0dcd03156-finance-assistant-centro-de-informacion-elgin</t>
+  </si>
+  <si>
+    <t>Forensic Accountant/Auditor, Investigate Complex Fraud(6465)</t>
+  </si>
+  <si>
+    <t>Mineola, New York</t>
+  </si>
+  <si>
+    <t>USD 76227.00 - 76227.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/ef1b564e518f4e19938dd40f4bacfac9-forensic-accountantauditor-investigate-complex-fraud6465-new-york-state-office-of-the-attorney-general-mineola</t>
+  </si>
+  <si>
+    <t>Forensic Accountant/Auditor, Investigate Complex Fraud(6466)</t>
+  </si>
+  <si>
+    <t>White Plains, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/46f6065bc6314dec9c193776f4b71684-forensic-accountantauditor-investigate-complex-fraud6466-new-york-state-office-of-the-attorney-general-white-plains</t>
+  </si>
+  <si>
+    <t>Fractional Fundraising and Development Consultant</t>
+  </si>
+  <si>
+    <t>Little Oaks Center for Neurodevelopment</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4e829935d7ef450db0c883ce6ccc6761-fractional-fundraising-and-development-consultant-little-oaks-center-for-neurodevelopment-new-york</t>
+  </si>
+  <si>
+    <t>Fractional IT Lead (Part-Time / Contract)</t>
+  </si>
+  <si>
+    <t>Esophageal Cancer Awareness Association (EC Aware)</t>
+  </si>
+  <si>
+    <t>USD 500.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine, Men, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/882217eff2e3495f9ce337da18c69e8c-fractional-it-lead-part-time-contract-esophageal-cancer-awareness-association-ec-aware-new-york</t>
+  </si>
+  <si>
+    <t>Grants Manager</t>
+  </si>
+  <si>
+    <t>Simons Foundation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b740f57bf5e347ce9597eef465208aba-grants-manager-simons-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Head of Programmes</t>
+  </si>
+  <si>
+    <t>SEED Madagascar</t>
+  </si>
+  <si>
+    <t>Taolagnaro, Anosy, MG</t>
+  </si>
+  <si>
+    <t>MGA 5000000.00 - 5000000.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa1eed498e414c38a00704c30eb45fa1-head-of-programmes-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
+    <t>Information &amp; Referral Specialist</t>
+  </si>
+  <si>
+    <t>USD 28.21 - 28.21/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c5737e89c35430d9e7ac2e9e2b98e76-information-referral-specialist-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Intake Assessor</t>
+  </si>
+  <si>
+    <t>Marlborough, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1952cf7ce1444f0986a6b26941e53512-intake-assessor-springwell-inc-marlborough</t>
+  </si>
+  <si>
+    <t>International Director 2027</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>USD 100.00 - 200.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/66eb6ca5504641d6a410b6a85f912bcf-international-director-2027-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>Land Preservation Grants Assistant</t>
+  </si>
+  <si>
+    <t>American Battlefield Trust</t>
+  </si>
+  <si>
+    <t>USD 46000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d945dd41706499e8118e7a668b7b9e2-land-preservation-grants-assistant-american-battlefield-trust-washington</t>
+  </si>
+  <si>
+    <t>Lead Staff Attorney Medical-Financial-Legal Partnership</t>
+  </si>
+  <si>
+    <t>Tzedek DC</t>
+  </si>
+  <si>
+    <t>USD 76000.00 - 119000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b31f65111d4f44b99b6099d7f5d29263-lead-staff-attorney-medical-financial-legal-partnership-tzedek-dc-washington</t>
+  </si>
+  <si>
+    <t>Major Donor Associate</t>
+  </si>
+  <si>
+    <t>Maryknoll Sisters</t>
+  </si>
+  <si>
+    <t>Ossining, New York</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a28d6ad0a4c421f98daa9f0e841ceca-major-donor-associate-maryknoll-sisters-ossining</t>
+  </si>
+  <si>
+    <t>Major Gifts and Planned Giving Manager</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Children Youth, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23bf39ea0ee74a50b8da72b8976e4fb7-major-gifts-and-planned-giving-manager-maryknoll-sisters-ossining</t>
+  </si>
+  <si>
+    <t>Manager of Fundraising Events</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7b3dae71a85482aad626d5b18fc90d8-manager-of-fundraising-events-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Managing Social Worker</t>
+  </si>
+  <si>
+    <t>Public Counsel</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b5042e73ac44e04a4124737beb7ee53-managing-social-worker-public-counsel-los-angeles</t>
+  </si>
+  <si>
+    <t>Media and Communications Officer</t>
+  </si>
+  <si>
+    <t>MGA 1800000.00 - 1800000.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a37609742c944948bbe7d887b928b94-media-and-communications-officer-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
+    <t>Member Mobilization &amp; Policy Specialist</t>
+  </si>
+  <si>
+    <t>Ohio Nurses Association</t>
+  </si>
+  <si>
+    <t>Columbus, OH</t>
+  </si>
+  <si>
+    <t>USD 64206.89/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60b802f207484d28898246b45e966de6-member-mobilization-policy-specialist-ohio-nurses-association-columbus</t>
+  </si>
+  <si>
+    <t>Mitigation Specialist, Second Look</t>
+  </si>
+  <si>
+    <t>Osborne Association Inc</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/31a9db96d19b44aa9bda4247f1624ee7-mitigation-specialist-second-look-osborne-association-inc-brooklyn</t>
+  </si>
+  <si>
+    <t>Museum Technology Support Engineer</t>
+  </si>
+  <si>
+    <t>National Geographic Society</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 80750.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac117ee98a8d4cd69f068fee2f9cb06f-museum-technology-support-engineer-national-geographic-society-washington</t>
+  </si>
+  <si>
+    <t>National Executive Assistant</t>
+  </si>
+  <si>
+    <t>After-School All-Stars</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Sports Recreation, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a9dd038d6544254b4c158c98fc2b742-national-executive-assistant-after-school-all-stars-los-angeles</t>
+  </si>
+  <si>
+    <t>Office of Special Investigation Legal Support Analyst (6467)</t>
+  </si>
+  <si>
+    <t>USD 69719.00 - 69719.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/d97d1bfd88434ed68921a6881a4260c4-office-of-special-investigation-legal-support-analyst-6467-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>P/T Preschool Teacher Assistant- East Orange Preschool</t>
+  </si>
+  <si>
+    <t>Metro YMCAs of the Oranges</t>
+  </si>
+  <si>
+    <t>East Orange, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 15000.00 - 20000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e4f9d3a81c34a2cb1d1ae5f7d8f4bbb-pt-preschool-teacher-assistant-east-orange-preschool-metro-ymcas-of-the-oranges-east-orange</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d78f891736234ce2a657be4b43700afa-paralegal-whistleblower-aid-washington</t>
+  </si>
+  <si>
+    <t>Paralegal - Detention &amp; Removal Defense</t>
+  </si>
+  <si>
+    <t>Legal Services of New Jersey</t>
+  </si>
+  <si>
+    <t>Edison, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 56000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23de5b6cd102403798ac23dc6772d93a-paralegal-detention-removal-defense-legal-services-of-new-jersey-edison</t>
+  </si>
+  <si>
+    <t>PERSONAL DE CUIDADO DE ADULTOS MAYORES</t>
+  </si>
+  <si>
+    <t>Hermanas de Don Orione</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6946385b56847bfb99ec82f407c9e33-personal-de-cuidado-de-adultos-mayores-hermanas-de-don-orione-buenos-aires</t>
+  </si>
+  <si>
+    <t>Political Director</t>
+  </si>
+  <si>
+    <t>Sunrise Movement</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9661263060bd4949b8c7ffbd79ea48d4-political-director-sunrise-movement-philadelphia</t>
+  </si>
+  <si>
+    <t>Program Associate, Institutional Grants</t>
+  </si>
+  <si>
+    <t>Tarbell Center for AI Journalism</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 112000.00/year</t>
+  </si>
+  <si>
+    <t>Science Technology, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f51cc7c7fc4b4e6993bcd4cb3c3902d1-program-associate-institutional-grants-tarbell-center-for-ai-journalism-claymont</t>
+  </si>
+  <si>
+    <t>Program Officer, Institutional Grants</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 171000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Media, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/62fc620eabd145f09ddb8b5e1e691fbc-program-officer-institutional-grants-tarbell-center-for-ai-journalism-claymont</t>
+  </si>
+  <si>
+    <t>Program Specialist, Reporting Grants</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 139000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6c7b8e7edef4fab82cd3cf4e524f2c0-program-specialist-reporting-grants-tarbell-center-for-ai-journalism-claymont</t>
+  </si>
+  <si>
+    <t>Programme Manager - Community Health</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f908ef48139a4f4fb1edb029de801a1d-programme-manager-community-health-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
+    <t>Programme Officer - Community Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0fb26764c0804a8e862e3a57e5c46234-programme-officer-community-health-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
+    <t>Programme Officer - Financial Resilience</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef624d9c7e7b4277b2d46ae4e1685e8c-programme-officer-financial-resilience-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
+    <t>Programs Specialist</t>
+  </si>
+  <si>
+    <t>National Hydropower Association</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 84000.00/year</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac902488b5ba4e13bcdeac02da43d3da-programs-specialist-national-hydropower-association-washington</t>
+  </si>
+  <si>
+    <t>Quality Improvement Manager</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/91b54fbdbdb64cf583d2269ce34bd6ee-quality-improvement-manager-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Receptionist</t>
+  </si>
+  <si>
+    <t>Greater Boston Legal Services</t>
+  </si>
+  <si>
+    <t>USD 47000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08442decade64cb1864110b55cef576d-receptionist-greater-boston-legal-services-boston</t>
+  </si>
+  <si>
+    <t>Registered Nurse (RN)</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e54a956000d24d2baf1face3f88debb5-registered-nurse-rn-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Restorative Practices Youth Training Specialist 1</t>
+  </si>
+  <si>
+    <t>Build 2 Lead</t>
+  </si>
+  <si>
+    <t>Federal Way, Washington</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4156acbbd434a75a6e975fa79dec5dd-restorative-practices-youth-training-specialist-1-build-2-lead-federal-way</t>
+  </si>
+  <si>
+    <t>Sea Turtle Conservation</t>
+  </si>
+  <si>
+    <t>ARCHELON, The Sea Turtle Protection Society of Greece</t>
+  </si>
+  <si>
+    <t>Rethimno, (no state), GR</t>
+  </si>
+  <si>
+    <t>Animals, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/139a4d00b7f74b3fb9fb6e68b539fc93-sea-turtle-conservation-archelon-the-sea-turtle-protection-society-of-greece-rethimno</t>
+  </si>
+  <si>
+    <t>Senior Advancement Officer</t>
+  </si>
+  <si>
+    <t>Policing Project</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4e26ae2482604c6e9053272bc7c393a2-senior-advancement-officer-policing-project-new-york</t>
+  </si>
+  <si>
+    <t>Senior Conservation Research Assistant (Madagascar)</t>
+  </si>
+  <si>
+    <t>Environment, Community Development, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6cff1d337b3448f9dcb07c904d54a6b-senior-conservation-research-assistant-madagascar-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
+    <t>Senior Counsel</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58c0bf015dd14a6cabe56545f80bfa3d-senior-counsel-whistleblower-aid-washington</t>
+  </si>
+  <si>
+    <t>Senior Director of Medicaid Policy</t>
+  </si>
+  <si>
+    <t>Center on Budget and Policy Priorities</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Poverty, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a8a5594750c463e9f71da43b1ba7858-senior-director-of-medicaid-policy-center-on-budget-and-policy-priorities-washington</t>
+  </si>
+  <si>
+    <t>Senior Director, Finance</t>
+  </si>
+  <si>
+    <t>Rebuilding Together</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4bd61922834145a68a80832c23f84db3-senior-director-finance-rebuilding-together-washington</t>
+  </si>
+  <si>
+    <t>Senior Director, Science (Perpetual Planet Expeditions)</t>
+  </si>
+  <si>
+    <t>USD 161500.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/01cb9cde90244e0eb5ba03e1060b095d-senior-director-science-perpetual-planet-expeditions-national-geographic-society-washington</t>
+  </si>
+  <si>
+    <t>Senior Manager of Workforce Development</t>
+  </si>
+  <si>
+    <t>MassHire Metro North Workforce Board</t>
+  </si>
+  <si>
+    <t>Malden, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 73941.00 - 81443.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b4a2012fe9842d4927c1fdca63b3598-senior-manager-of-workforce-development-masshire-metro-north-workforce-board-malden</t>
+  </si>
+  <si>
+    <t>Senior Manager/Associate Director, Funding the Next Generation (FNG)</t>
+  </si>
+  <si>
+    <t>Childrens Funding Project</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 113750.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf63497a8f784894b6f6833bf9fa067c-senior-managerassociate-director-funding-the-next-generation-fng-childrens-funding-project-washington</t>
+  </si>
+  <si>
+    <t>Senior Rackets Investigator</t>
+  </si>
+  <si>
+    <t>City of New York</t>
+  </si>
+  <si>
+    <t>USD 74437.00 - 74437.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/d4a2f13356624b408ff09db47c061fe3-senior-rackets-investigator-city-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Senior Staff Accountant</t>
+  </si>
+  <si>
+    <t>Popular Democracy</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/512832b2473f42528e96dfc507afe13a-senior-staff-accountant-popular-democracy-brooklyn</t>
+  </si>
+  <si>
+    <t>Small Business Consultant</t>
+  </si>
+  <si>
+    <t>Communities Unlimited, Inc.</t>
+  </si>
+  <si>
+    <t>Remote (Jackson, Mississippi)</t>
+  </si>
+  <si>
+    <t>USD 61800.00 - 63500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4e76b7c0a8fe4b019da50d92333ac40f-small-business-consultant-communities-unlimited-inc-jackson</t>
+  </si>
+  <si>
+    <t>Social Worker – Detention &amp; Removal Defense</t>
+  </si>
+  <si>
+    <t>USD 58000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de3e46db914040c9ba291d3a5a493090-social-worker-detention-removal-defense-legal-services-of-new-jersey-edison</t>
+  </si>
+  <si>
+    <t>Solutions Manager</t>
+  </si>
+  <si>
+    <t>JobsFirst NEPA</t>
+  </si>
+  <si>
+    <t>Scranton, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35361a6c455b4b69bceb6fdfb2bbddbf-solutions-manager-jobsfirst-nepa-scranton</t>
+  </si>
+  <si>
+    <t>Southeast Region Lands Project Manager</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bfa60552e0d74c8a86cf3e739ff23735-southeast-region-lands-project-manager-american-battlefield-trust-washington</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>The Waterfront Project, Inc.</t>
+  </si>
+  <si>
+    <t>Jersey City, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 82500.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b71357e820f4c1b90963449ef9411a7-staff-attorney-the-waterfront-project-inc-jersey-city</t>
+  </si>
+  <si>
+    <t>Staff Attorney – Detention &amp; Removal Defense</t>
+  </si>
+  <si>
+    <t>USD 82000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/250b3bced20f4a828f04006b70c210fb-staff-attorney-detention-removal-defense-legal-services-of-new-jersey-edison</t>
+  </si>
+  <si>
+    <t>Supervising Rackets Investigator</t>
+  </si>
+  <si>
+    <t>USD 78699.00 - 109743.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/f453b0a034ea45dbb2175fd01309d030-supervising-rackets-investigator-city-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be48a18ff4e74940a77740794cd91baf-supervisor-springwell-inc-waltham</t>
+  </si>
+  <si>
+    <t>Vice President of Horticulture</t>
+  </si>
+  <si>
+    <t>Missouri Botanical Garden</t>
+  </si>
+  <si>
+    <t>St. Louis, Missouri</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1a09f8ffb8064546b08b2e9585e7a651-vice-president-of-horticulture-missouri-botanical-garden-st-louis</t>
+  </si>
+  <si>
+    <t>Village Director</t>
+  </si>
+  <si>
+    <t>Viva Village</t>
+  </si>
+  <si>
+    <t>Beaverton, Oregon</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Seniors Retirement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60205adfbce5478bb5e68c90ed2f848d-village-director-viva-village-beaverton</t>
+  </si>
+  <si>
+    <t>Volunteer Recruitment &amp; Engagement Manager</t>
+  </si>
+  <si>
+    <t>Ronald McDonald House Philadelphia</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 69000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9731a844ea364c96af6aa47c0deb7737-volunteer-recruitment-engagement-manager-ronald-mcdonald-house-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Youth Workforce Manager</t>
+  </si>
+  <si>
+    <t>USD 67512.00 - 73941.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a55b77504bc48cf82f055969f5f60a0-youth-workforce-manager-masshire-metro-north-workforce-board-malden</t>
   </si>
 </sst>
 </file>
@@ -456,7 +2232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -495,8 +2271,541 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" t="s">
+        <v>102</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" t="s">
+        <v>112</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F22" t="s">
+        <v>118</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -504,7 +2813,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -543,8 +2852,37 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -552,7 +2890,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -593,48 +2931,2420 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>136</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>144</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>18</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" t="s">
+        <v>179</v>
+      </c>
+      <c r="F11" t="s">
+        <v>180</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" t="s">
+        <v>185</v>
+      </c>
+      <c r="F12" t="s">
+        <v>186</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F13" t="s">
+        <v>192</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>194</v>
+      </c>
+      <c r="B14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D14" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" t="s">
+        <v>197</v>
+      </c>
+      <c r="F14" t="s">
+        <v>198</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" t="s">
+        <v>203</v>
+      </c>
+      <c r="F15" t="s">
+        <v>204</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E16" t="s">
+        <v>207</v>
+      </c>
+      <c r="F16" t="s">
+        <v>198</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" t="s">
+        <v>214</v>
+      </c>
+      <c r="D18" t="s">
+        <v>149</v>
+      </c>
+      <c r="E18" t="s">
+        <v>215</v>
+      </c>
+      <c r="F18" t="s">
+        <v>216</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>218</v>
+      </c>
+      <c r="B19" t="s">
+        <v>219</v>
+      </c>
+      <c r="C19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" t="s">
+        <v>142</v>
+      </c>
+      <c r="E19" t="s">
+        <v>220</v>
+      </c>
+      <c r="F19" t="s">
+        <v>221</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>223</v>
+      </c>
+      <c r="B20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" t="s">
+        <v>225</v>
+      </c>
+      <c r="D20" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" t="s">
+        <v>226</v>
+      </c>
+      <c r="F20" t="s">
+        <v>227</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>229</v>
+      </c>
+      <c r="B21" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" t="s">
+        <v>202</v>
+      </c>
+      <c r="D21" t="s">
+        <v>142</v>
+      </c>
+      <c r="E21" t="s">
+        <v>231</v>
+      </c>
+      <c r="F21" t="s">
+        <v>232</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>234</v>
+      </c>
+      <c r="B22" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" t="s">
+        <v>178</v>
+      </c>
+      <c r="D22" t="s">
+        <v>142</v>
+      </c>
+      <c r="E22" t="s">
+        <v>235</v>
+      </c>
+      <c r="F22" t="s">
+        <v>180</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>237</v>
+      </c>
+      <c r="B23" t="s">
+        <v>238</v>
+      </c>
+      <c r="C23" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" t="s">
+        <v>240</v>
+      </c>
+      <c r="F23" t="s">
+        <v>241</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>243</v>
+      </c>
+      <c r="B24" t="s">
+        <v>244</v>
+      </c>
+      <c r="C24" t="s">
+        <v>245</v>
+      </c>
+      <c r="D24" t="s">
+        <v>184</v>
+      </c>
+      <c r="E24" t="s">
+        <v>246</v>
+      </c>
+      <c r="F24" t="s">
+        <v>247</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>249</v>
+      </c>
+      <c r="B25" t="s">
+        <v>250</v>
+      </c>
+      <c r="C25" t="s">
+        <v>251</v>
+      </c>
+      <c r="D25" t="s">
+        <v>142</v>
+      </c>
+      <c r="E25" t="s">
+        <v>252</v>
+      </c>
+      <c r="F25" t="s">
+        <v>253</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>255</v>
+      </c>
+      <c r="B26" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" t="s">
+        <v>257</v>
+      </c>
+      <c r="D26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E26" t="s">
+        <v>258</v>
+      </c>
+      <c r="F26" t="s">
+        <v>128</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>260</v>
+      </c>
+      <c r="B27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C27" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" t="s">
+        <v>142</v>
+      </c>
+      <c r="E27" t="s">
+        <v>263</v>
+      </c>
+      <c r="F27" t="s">
+        <v>264</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>266</v>
+      </c>
+      <c r="B28" t="s">
+        <v>267</v>
+      </c>
+      <c r="C28" t="s">
+        <v>268</v>
+      </c>
+      <c r="D28" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28" t="s">
+        <v>269</v>
+      </c>
+      <c r="F28" t="s">
+        <v>270</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>266</v>
+      </c>
+      <c r="B29" t="s">
+        <v>272</v>
+      </c>
+      <c r="C29" t="s">
+        <v>273</v>
+      </c>
+      <c r="D29" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" t="s">
+        <v>274</v>
+      </c>
+      <c r="F29" t="s">
+        <v>275</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>266</v>
+      </c>
+      <c r="B30" t="s">
+        <v>277</v>
+      </c>
+      <c r="C30" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" t="s">
+        <v>278</v>
+      </c>
+      <c r="F30" t="s">
+        <v>279</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>281</v>
+      </c>
+      <c r="B31" t="s">
+        <v>282</v>
+      </c>
+      <c r="C31" t="s">
+        <v>283</v>
+      </c>
+      <c r="D31" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31" t="s">
+        <v>284</v>
+      </c>
+      <c r="F31" t="s">
+        <v>285</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>287</v>
+      </c>
+      <c r="B32" t="s">
+        <v>288</v>
+      </c>
+      <c r="C32" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" t="s">
+        <v>289</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>291</v>
+      </c>
+      <c r="B33" t="s">
+        <v>292</v>
+      </c>
+      <c r="C33" t="s">
+        <v>239</v>
+      </c>
+      <c r="D33" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" t="s">
+        <v>293</v>
+      </c>
+      <c r="F33" t="s">
+        <v>128</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>295</v>
+      </c>
+      <c r="B34" t="s">
+        <v>296</v>
+      </c>
+      <c r="C34" t="s">
+        <v>297</v>
+      </c>
+      <c r="D34" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" t="s">
+        <v>298</v>
+      </c>
+      <c r="F34" t="s">
+        <v>299</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>301</v>
+      </c>
+      <c r="B35" t="s">
+        <v>296</v>
+      </c>
+      <c r="C35" t="s">
+        <v>302</v>
+      </c>
+      <c r="D35" t="s">
+        <v>142</v>
+      </c>
+      <c r="E35" t="s">
+        <v>298</v>
+      </c>
+      <c r="F35" t="s">
+        <v>299</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>304</v>
+      </c>
+      <c r="B36" t="s">
+        <v>305</v>
+      </c>
+      <c r="C36" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36" t="s">
+        <v>142</v>
+      </c>
+      <c r="E36" t="s">
+        <v>220</v>
+      </c>
+      <c r="F36" t="s">
+        <v>306</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>304</v>
+      </c>
+      <c r="B37" t="s">
+        <v>308</v>
+      </c>
+      <c r="C37" t="s">
+        <v>309</v>
+      </c>
+      <c r="D37" t="s">
+        <v>142</v>
+      </c>
+      <c r="E37" t="s">
+        <v>310</v>
+      </c>
+      <c r="F37" t="s">
+        <v>311</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" t="s">
+        <v>313</v>
+      </c>
+      <c r="C38" t="s">
+        <v>314</v>
+      </c>
+      <c r="D38" t="s">
+        <v>142</v>
+      </c>
+      <c r="E38" t="s">
+        <v>315</v>
+      </c>
+      <c r="F38" t="s">
+        <v>316</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" t="s">
+        <v>318</v>
+      </c>
+      <c r="C39" t="s">
+        <v>319</v>
+      </c>
+      <c r="D39" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" t="s">
+        <v>320</v>
+      </c>
+      <c r="F39" t="s">
+        <v>198</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" t="s">
+        <v>322</v>
+      </c>
+      <c r="C40" t="s">
+        <v>323</v>
+      </c>
+      <c r="D40" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40" t="s">
+        <v>324</v>
+      </c>
+      <c r="F40" t="s">
+        <v>325</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" t="s">
+        <v>327</v>
+      </c>
+      <c r="C41" t="s">
+        <v>328</v>
+      </c>
+      <c r="D41" t="s">
+        <v>142</v>
+      </c>
+      <c r="E41" t="s">
+        <v>329</v>
+      </c>
+      <c r="F41" t="s">
+        <v>330</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" t="s">
+        <v>332</v>
+      </c>
+      <c r="C42" t="s">
+        <v>333</v>
+      </c>
+      <c r="D42" t="s">
+        <v>184</v>
+      </c>
+      <c r="E42" t="s">
+        <v>334</v>
+      </c>
+      <c r="F42" t="s">
+        <v>335</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" t="s">
+        <v>337</v>
+      </c>
+      <c r="F43" t="s">
+        <v>338</v>
+      </c>
+      <c r="G43" t="s">
+        <v>339</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>341</v>
+      </c>
+      <c r="B44" t="s">
+        <v>342</v>
+      </c>
+      <c r="C44" t="s">
+        <v>202</v>
+      </c>
+      <c r="D44" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" t="s">
+        <v>343</v>
+      </c>
+      <c r="F44" t="s">
+        <v>344</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>346</v>
+      </c>
+      <c r="B45" t="s">
+        <v>347</v>
+      </c>
+      <c r="C45" t="s">
+        <v>162</v>
+      </c>
+      <c r="D45" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" t="s">
+        <v>240</v>
+      </c>
+      <c r="F45" t="s">
+        <v>348</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>350</v>
+      </c>
+      <c r="B46" t="s">
+        <v>351</v>
+      </c>
+      <c r="C46" t="s">
+        <v>352</v>
+      </c>
+      <c r="D46" t="s">
+        <v>142</v>
+      </c>
+      <c r="E46" t="s">
+        <v>353</v>
+      </c>
+      <c r="F46" t="s">
+        <v>354</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>356</v>
+      </c>
+      <c r="B47" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" t="s">
+        <v>357</v>
+      </c>
+      <c r="D47" t="s">
+        <v>142</v>
+      </c>
+      <c r="E47" t="s">
+        <v>358</v>
+      </c>
+      <c r="F47" t="s">
+        <v>128</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>360</v>
+      </c>
+      <c r="B48" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" t="s">
+        <v>361</v>
+      </c>
+      <c r="D48" t="s">
+        <v>142</v>
+      </c>
+      <c r="E48" t="s">
+        <v>358</v>
+      </c>
+      <c r="F48" t="s">
+        <v>128</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>363</v>
+      </c>
+      <c r="B49" t="s">
+        <v>364</v>
+      </c>
+      <c r="C49" t="s">
+        <v>167</v>
+      </c>
+      <c r="D49" t="s">
+        <v>149</v>
+      </c>
+      <c r="E49" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" t="s">
+        <v>365</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>367</v>
+      </c>
+      <c r="B50" t="s">
+        <v>368</v>
+      </c>
+      <c r="C50" t="s">
+        <v>202</v>
+      </c>
+      <c r="D50" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50" t="s">
+        <v>369</v>
+      </c>
+      <c r="F50" t="s">
+        <v>370</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>372</v>
+      </c>
+      <c r="B51" t="s">
+        <v>373</v>
+      </c>
+      <c r="C51" t="s">
+        <v>167</v>
+      </c>
+      <c r="D51" t="s">
+        <v>142</v>
+      </c>
+      <c r="E51" t="s">
+        <v>337</v>
+      </c>
+      <c r="F51" t="s">
+        <v>128</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>375</v>
+      </c>
+      <c r="B52" t="s">
+        <v>376</v>
+      </c>
+      <c r="C52" t="s">
+        <v>377</v>
+      </c>
+      <c r="D52" t="s">
+        <v>135</v>
+      </c>
+      <c r="E52" t="s">
+        <v>378</v>
+      </c>
+      <c r="F52" t="s">
+        <v>379</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>381</v>
+      </c>
+      <c r="B53" t="s">
+        <v>177</v>
+      </c>
+      <c r="C53" t="s">
+        <v>178</v>
+      </c>
+      <c r="D53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" t="s">
+        <v>382</v>
+      </c>
+      <c r="F53" t="s">
+        <v>180</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>384</v>
+      </c>
+      <c r="B54" t="s">
+        <v>177</v>
+      </c>
+      <c r="C54" t="s">
+        <v>385</v>
+      </c>
+      <c r="D54" t="s">
+        <v>142</v>
+      </c>
+      <c r="E54" t="s">
+        <v>382</v>
+      </c>
+      <c r="F54" t="s">
+        <v>180</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>387</v>
+      </c>
+      <c r="B55" t="s">
+        <v>388</v>
+      </c>
+      <c r="C55" t="s">
+        <v>202</v>
+      </c>
+      <c r="D55" t="s">
+        <v>149</v>
+      </c>
+      <c r="E55" t="s">
+        <v>389</v>
+      </c>
+      <c r="F55" t="s">
+        <v>390</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>392</v>
+      </c>
+      <c r="B56" t="s">
+        <v>393</v>
+      </c>
+      <c r="C56" t="s">
+        <v>162</v>
+      </c>
+      <c r="D56" t="s">
+        <v>142</v>
+      </c>
+      <c r="E56" t="s">
+        <v>394</v>
+      </c>
+      <c r="F56" t="s">
+        <v>395</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>397</v>
+      </c>
+      <c r="B57" t="s">
+        <v>398</v>
+      </c>
+      <c r="C57" t="s">
+        <v>162</v>
+      </c>
+      <c r="D57" t="s">
+        <v>142</v>
+      </c>
+      <c r="E57" t="s">
+        <v>399</v>
+      </c>
+      <c r="F57" t="s">
+        <v>400</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>402</v>
+      </c>
+      <c r="B58" t="s">
+        <v>403</v>
+      </c>
+      <c r="C58" t="s">
+        <v>404</v>
+      </c>
+      <c r="D58" t="s">
+        <v>142</v>
+      </c>
+      <c r="E58" t="s">
+        <v>405</v>
+      </c>
+      <c r="F58" t="s">
+        <v>406</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>408</v>
+      </c>
+      <c r="B59" t="s">
+        <v>403</v>
+      </c>
+      <c r="C59" t="s">
+        <v>404</v>
+      </c>
+      <c r="D59" t="s">
+        <v>142</v>
+      </c>
+      <c r="E59" t="s">
+        <v>409</v>
+      </c>
+      <c r="F59" t="s">
+        <v>410</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>412</v>
+      </c>
+      <c r="B60" t="s">
+        <v>219</v>
+      </c>
+      <c r="C60" t="s">
+        <v>202</v>
+      </c>
+      <c r="D60" t="s">
+        <v>142</v>
+      </c>
+      <c r="E60" t="s">
+        <v>413</v>
+      </c>
+      <c r="F60" t="s">
+        <v>221</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>415</v>
+      </c>
+      <c r="B61" t="s">
+        <v>416</v>
+      </c>
+      <c r="C61" t="s">
+        <v>417</v>
+      </c>
+      <c r="D61" t="s">
+        <v>142</v>
+      </c>
+      <c r="E61" t="s">
+        <v>418</v>
+      </c>
+      <c r="F61" t="s">
+        <v>164</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>420</v>
+      </c>
+      <c r="B62" t="s">
+        <v>376</v>
+      </c>
+      <c r="C62" t="s">
+        <v>377</v>
+      </c>
+      <c r="D62" t="s">
+        <v>142</v>
+      </c>
+      <c r="E62" t="s">
+        <v>421</v>
+      </c>
+      <c r="F62" t="s">
+        <v>379</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>423</v>
+      </c>
+      <c r="B63" t="s">
+        <v>424</v>
+      </c>
+      <c r="C63" t="s">
+        <v>425</v>
+      </c>
+      <c r="D63" t="s">
+        <v>142</v>
+      </c>
+      <c r="E63" t="s">
+        <v>426</v>
+      </c>
+      <c r="F63" t="s">
+        <v>427</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>429</v>
+      </c>
+      <c r="B64" t="s">
+        <v>430</v>
+      </c>
+      <c r="C64" t="s">
+        <v>431</v>
+      </c>
+      <c r="D64" t="s">
+        <v>142</v>
+      </c>
+      <c r="E64" t="s">
+        <v>432</v>
+      </c>
+      <c r="F64" t="s">
+        <v>128</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>434</v>
+      </c>
+      <c r="B65" t="s">
+        <v>435</v>
+      </c>
+      <c r="C65" t="s">
+        <v>436</v>
+      </c>
+      <c r="D65" t="s">
+        <v>142</v>
+      </c>
+      <c r="E65" t="s">
+        <v>437</v>
+      </c>
+      <c r="F65" t="s">
+        <v>438</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>440</v>
+      </c>
+      <c r="B66" t="s">
+        <v>441</v>
+      </c>
+      <c r="C66" t="s">
+        <v>442</v>
+      </c>
+      <c r="D66" t="s">
+        <v>142</v>
+      </c>
+      <c r="E66" t="s">
+        <v>443</v>
+      </c>
+      <c r="F66" t="s">
+        <v>444</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>446</v>
+      </c>
+      <c r="B67" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" t="s">
+        <v>167</v>
+      </c>
+      <c r="D67" t="s">
+        <v>142</v>
+      </c>
+      <c r="E67" t="s">
+        <v>447</v>
+      </c>
+      <c r="F67" t="s">
+        <v>128</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>449</v>
+      </c>
+      <c r="B68" t="s">
+        <v>450</v>
+      </c>
+      <c r="C68" t="s">
+        <v>451</v>
+      </c>
+      <c r="D68" t="s">
+        <v>184</v>
+      </c>
+      <c r="E68" t="s">
+        <v>452</v>
+      </c>
+      <c r="F68" t="s">
+        <v>453</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>455</v>
+      </c>
+      <c r="B69" t="s">
+        <v>161</v>
+      </c>
+      <c r="C69" t="s">
+        <v>162</v>
+      </c>
+      <c r="D69" t="s">
+        <v>149</v>
+      </c>
+      <c r="E69" t="s">
+        <v>413</v>
+      </c>
+      <c r="F69" t="s">
+        <v>164</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>457</v>
+      </c>
+      <c r="B70" t="s">
+        <v>458</v>
+      </c>
+      <c r="C70" t="s">
+        <v>459</v>
+      </c>
+      <c r="D70" t="s">
+        <v>142</v>
+      </c>
+      <c r="E70" t="s">
+        <v>460</v>
+      </c>
+      <c r="F70" t="s">
+        <v>164</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>462</v>
+      </c>
+      <c r="B71" t="s">
+        <v>463</v>
+      </c>
+      <c r="C71" t="s">
+        <v>464</v>
+      </c>
+      <c r="D71" t="s">
+        <v>135</v>
+      </c>
+      <c r="E71" t="s">
+        <v>128</v>
+      </c>
+      <c r="F71" t="s">
+        <v>465</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>467</v>
+      </c>
+      <c r="B72" t="s">
+        <v>468</v>
+      </c>
+      <c r="C72" t="s">
+        <v>202</v>
+      </c>
+      <c r="D72" t="s">
+        <v>142</v>
+      </c>
+      <c r="E72" t="s">
+        <v>324</v>
+      </c>
+      <c r="F72" t="s">
+        <v>469</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>471</v>
+      </c>
+      <c r="B73" t="s">
+        <v>472</v>
+      </c>
+      <c r="C73" t="s">
+        <v>202</v>
+      </c>
+      <c r="D73" t="s">
+        <v>142</v>
+      </c>
+      <c r="E73" t="s">
+        <v>473</v>
+      </c>
+      <c r="F73" t="s">
+        <v>474</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>476</v>
+      </c>
+      <c r="B74" t="s">
+        <v>472</v>
+      </c>
+      <c r="C74" t="s">
+        <v>202</v>
+      </c>
+      <c r="D74" t="s">
+        <v>142</v>
+      </c>
+      <c r="E74" t="s">
+        <v>477</v>
+      </c>
+      <c r="F74" t="s">
+        <v>478</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>480</v>
+      </c>
+      <c r="B75" t="s">
+        <v>472</v>
+      </c>
+      <c r="C75" t="s">
+        <v>202</v>
+      </c>
+      <c r="D75" t="s">
+        <v>142</v>
+      </c>
+      <c r="E75" t="s">
+        <v>481</v>
+      </c>
+      <c r="F75" t="s">
+        <v>474</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>483</v>
+      </c>
+      <c r="B76" t="s">
+        <v>376</v>
+      </c>
+      <c r="C76" t="s">
+        <v>377</v>
+      </c>
+      <c r="D76" t="s">
+        <v>142</v>
+      </c>
+      <c r="E76" t="s">
+        <v>128</v>
+      </c>
+      <c r="F76" t="s">
+        <v>484</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>486</v>
+      </c>
+      <c r="B77" t="s">
+        <v>376</v>
+      </c>
+      <c r="C77" t="s">
+        <v>377</v>
+      </c>
+      <c r="D77" t="s">
+        <v>142</v>
+      </c>
+      <c r="E77" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77" t="s">
+        <v>379</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>488</v>
+      </c>
+      <c r="B78" t="s">
+        <v>376</v>
+      </c>
+      <c r="C78" t="s">
+        <v>377</v>
+      </c>
+      <c r="D78" t="s">
+        <v>142</v>
+      </c>
+      <c r="E78" t="s">
+        <v>128</v>
+      </c>
+      <c r="F78" t="s">
+        <v>379</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>490</v>
+      </c>
+      <c r="B79" t="s">
+        <v>491</v>
+      </c>
+      <c r="C79" t="s">
+        <v>162</v>
+      </c>
+      <c r="D79" t="s">
+        <v>142</v>
+      </c>
+      <c r="E79" t="s">
+        <v>492</v>
+      </c>
+      <c r="F79" t="s">
+        <v>493</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>495</v>
+      </c>
+      <c r="B80" t="s">
+        <v>177</v>
+      </c>
+      <c r="C80" t="s">
+        <v>178</v>
+      </c>
+      <c r="D80" t="s">
+        <v>142</v>
+      </c>
+      <c r="E80" t="s">
+        <v>496</v>
+      </c>
+      <c r="F80" t="s">
+        <v>180</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>498</v>
+      </c>
+      <c r="B81" t="s">
+        <v>499</v>
+      </c>
+      <c r="C81" t="s">
+        <v>239</v>
+      </c>
+      <c r="D81" t="s">
+        <v>142</v>
+      </c>
+      <c r="E81" t="s">
+        <v>500</v>
+      </c>
+      <c r="F81" t="s">
+        <v>164</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>502</v>
+      </c>
+      <c r="B82" t="s">
+        <v>177</v>
+      </c>
+      <c r="C82" t="s">
+        <v>178</v>
+      </c>
+      <c r="D82" t="s">
+        <v>142</v>
+      </c>
+      <c r="E82" t="s">
+        <v>503</v>
+      </c>
+      <c r="F82" t="s">
+        <v>180</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>505</v>
+      </c>
+      <c r="B83" t="s">
+        <v>506</v>
+      </c>
+      <c r="C83" t="s">
+        <v>507</v>
+      </c>
+      <c r="D83" t="s">
+        <v>142</v>
+      </c>
+      <c r="E83" t="s">
+        <v>508</v>
+      </c>
+      <c r="F83" t="s">
+        <v>137</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>510</v>
+      </c>
+      <c r="B84" t="s">
+        <v>511</v>
+      </c>
+      <c r="C84" t="s">
+        <v>512</v>
+      </c>
+      <c r="D84" t="s">
+        <v>135</v>
+      </c>
+      <c r="E84" t="s">
+        <v>128</v>
+      </c>
+      <c r="F84" t="s">
+        <v>513</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>515</v>
+      </c>
+      <c r="B85" t="s">
+        <v>516</v>
+      </c>
+      <c r="C85" t="s">
+        <v>167</v>
+      </c>
+      <c r="D85" t="s">
+        <v>142</v>
+      </c>
+      <c r="E85" t="s">
+        <v>517</v>
+      </c>
+      <c r="F85" t="s">
+        <v>518</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>520</v>
+      </c>
+      <c r="B86" t="s">
+        <v>376</v>
+      </c>
+      <c r="C86" t="s">
+        <v>377</v>
+      </c>
+      <c r="D86" t="s">
+        <v>142</v>
+      </c>
+      <c r="E86" t="s">
+        <v>128</v>
+      </c>
+      <c r="F86" t="s">
+        <v>521</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>523</v>
+      </c>
+      <c r="B87" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" t="s">
+        <v>162</v>
+      </c>
+      <c r="D87" t="s">
+        <v>142</v>
+      </c>
+      <c r="E87" t="s">
+        <v>524</v>
+      </c>
+      <c r="F87" t="s">
+        <v>164</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>526</v>
+      </c>
+      <c r="B88" t="s">
+        <v>527</v>
+      </c>
+      <c r="C88" t="s">
+        <v>162</v>
+      </c>
+      <c r="D88" t="s">
+        <v>142</v>
+      </c>
+      <c r="E88" t="s">
+        <v>528</v>
+      </c>
+      <c r="F88" t="s">
+        <v>529</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>531</v>
+      </c>
+      <c r="B89" t="s">
+        <v>532</v>
+      </c>
+      <c r="C89" t="s">
+        <v>202</v>
+      </c>
+      <c r="D89" t="s">
+        <v>142</v>
+      </c>
+      <c r="E89" t="s">
+        <v>533</v>
+      </c>
+      <c r="F89" t="s">
+        <v>534</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>536</v>
+      </c>
+      <c r="B90" t="s">
+        <v>435</v>
+      </c>
+      <c r="C90" t="s">
+        <v>436</v>
+      </c>
+      <c r="D90" t="s">
+        <v>142</v>
+      </c>
+      <c r="E90" t="s">
+        <v>537</v>
+      </c>
+      <c r="F90" t="s">
+        <v>438</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>539</v>
+      </c>
+      <c r="B91" t="s">
+        <v>540</v>
+      </c>
+      <c r="C91" t="s">
+        <v>541</v>
+      </c>
+      <c r="D91" t="s">
+        <v>142</v>
+      </c>
+      <c r="E91" t="s">
+        <v>542</v>
+      </c>
+      <c r="F91" t="s">
+        <v>543</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>545</v>
+      </c>
+      <c r="B92" t="s">
+        <v>546</v>
+      </c>
+      <c r="C92" t="s">
+        <v>547</v>
+      </c>
+      <c r="D92" t="s">
+        <v>142</v>
+      </c>
+      <c r="E92" t="s">
+        <v>548</v>
+      </c>
+      <c r="F92" t="s">
+        <v>549</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>551</v>
+      </c>
+      <c r="B93" t="s">
+        <v>552</v>
+      </c>
+      <c r="C93" t="s">
+        <v>167</v>
+      </c>
+      <c r="D93" t="s">
+        <v>142</v>
+      </c>
+      <c r="E93" t="s">
+        <v>553</v>
+      </c>
+      <c r="F93" t="s">
+        <v>306</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>555</v>
+      </c>
+      <c r="B94" t="s">
+        <v>556</v>
+      </c>
+      <c r="C94" t="s">
+        <v>202</v>
+      </c>
+      <c r="D94" t="s">
+        <v>142</v>
+      </c>
+      <c r="E94" t="s">
+        <v>557</v>
+      </c>
+      <c r="F94" t="s">
+        <v>558</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>560</v>
+      </c>
+      <c r="B95" t="s">
+        <v>561</v>
+      </c>
+      <c r="C95" t="s">
+        <v>562</v>
+      </c>
+      <c r="D95" t="s">
+        <v>142</v>
+      </c>
+      <c r="E95" t="s">
+        <v>563</v>
+      </c>
+      <c r="F95" t="s">
+        <v>128</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>565</v>
+      </c>
+      <c r="B96" t="s">
+        <v>458</v>
+      </c>
+      <c r="C96" t="s">
+        <v>459</v>
+      </c>
+      <c r="D96" t="s">
+        <v>142</v>
+      </c>
+      <c r="E96" t="s">
+        <v>566</v>
+      </c>
+      <c r="F96" t="s">
+        <v>164</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>568</v>
+      </c>
+      <c r="B97" t="s">
+        <v>569</v>
+      </c>
+      <c r="C97" t="s">
+        <v>570</v>
+      </c>
+      <c r="D97" t="s">
+        <v>142</v>
+      </c>
+      <c r="E97" t="s">
+        <v>571</v>
+      </c>
+      <c r="F97" t="s">
+        <v>558</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>573</v>
+      </c>
+      <c r="B98" t="s">
+        <v>393</v>
+      </c>
+      <c r="C98" t="s">
+        <v>202</v>
+      </c>
+      <c r="D98" t="s">
+        <v>142</v>
+      </c>
+      <c r="E98" t="s">
+        <v>574</v>
+      </c>
+      <c r="F98" t="s">
+        <v>395</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>576</v>
+      </c>
+      <c r="B99" t="s">
+        <v>577</v>
+      </c>
+      <c r="C99" t="s">
+        <v>578</v>
+      </c>
+      <c r="D99" t="s">
+        <v>142</v>
+      </c>
+      <c r="E99" t="s">
+        <v>579</v>
+      </c>
+      <c r="F99" t="s">
+        <v>580</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>582</v>
+      </c>
+      <c r="B100" t="s">
+        <v>458</v>
+      </c>
+      <c r="C100" t="s">
+        <v>459</v>
+      </c>
+      <c r="D100" t="s">
+        <v>142</v>
+      </c>
+      <c r="E100" t="s">
+        <v>583</v>
+      </c>
+      <c r="F100" t="s">
+        <v>164</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>585</v>
+      </c>
+      <c r="B101" t="s">
+        <v>552</v>
+      </c>
+      <c r="C101" t="s">
+        <v>167</v>
+      </c>
+      <c r="D101" t="s">
+        <v>142</v>
+      </c>
+      <c r="E101" t="s">
+        <v>586</v>
+      </c>
+      <c r="F101" t="s">
+        <v>306</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>588</v>
+      </c>
+      <c r="B102" t="s">
+        <v>177</v>
+      </c>
+      <c r="C102" t="s">
+        <v>178</v>
+      </c>
+      <c r="D102" t="s">
+        <v>142</v>
+      </c>
+      <c r="E102" t="s">
+        <v>589</v>
+      </c>
+      <c r="F102" t="s">
+        <v>180</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>591</v>
+      </c>
+      <c r="B103" t="s">
+        <v>592</v>
+      </c>
+      <c r="C103" t="s">
+        <v>593</v>
+      </c>
+      <c r="D103" t="s">
+        <v>142</v>
+      </c>
+      <c r="E103" t="s">
+        <v>594</v>
+      </c>
+      <c r="F103" t="s">
+        <v>128</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>596</v>
+      </c>
+      <c r="B104" t="s">
+        <v>597</v>
+      </c>
+      <c r="C104" t="s">
+        <v>598</v>
+      </c>
+      <c r="D104" t="s">
+        <v>142</v>
+      </c>
+      <c r="E104" t="s">
+        <v>599</v>
+      </c>
+      <c r="F104" t="s">
+        <v>600</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>602</v>
+      </c>
+      <c r="B105" t="s">
+        <v>603</v>
+      </c>
+      <c r="C105" t="s">
+        <v>604</v>
+      </c>
+      <c r="D105" t="s">
+        <v>142</v>
+      </c>
+      <c r="E105" t="s">
+        <v>605</v>
+      </c>
+      <c r="F105" t="s">
+        <v>606</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>608</v>
+      </c>
+      <c r="B106" t="s">
+        <v>540</v>
+      </c>
+      <c r="C106" t="s">
+        <v>541</v>
+      </c>
+      <c r="D106" t="s">
+        <v>142</v>
+      </c>
+      <c r="E106" t="s">
+        <v>609</v>
+      </c>
+      <c r="F106" t="s">
+        <v>543</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>610</v>
       </c>
     </row>
   </sheetData>
@@ -642,6 +5352,109 @@
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-27.xlsx
+++ b/docs/xlsx/jobs-2026-10-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="798">
   <si>
     <t>Title</t>
   </si>
@@ -412,6 +412,45 @@
     <t>https://greenjobs.greenjobsearch.org/jobs/finance-accounting-manager/</t>
   </si>
   <si>
+    <t>SENIOR GARDENER</t>
+  </si>
+  <si>
+    <t>The Trust for Governors Island</t>
+  </si>
+  <si>
+    <t>New York, New York, United States</t>
+  </si>
+  <si>
+    <t>60,000 - 80,000</t>
+  </si>
+  <si>
+    <t>Horticulture / Gardening / Landscaping</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/senior-gardener/</t>
+  </si>
+  <si>
+    <t>ACCOUNTANT</t>
+  </si>
+  <si>
+    <t>Trust for Governors Island</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Urban Areas, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d33419b8858d48b5a4565a17704aabed-accountant-trust-for-governors-island-new-york</t>
+  </si>
+  <si>
     <t>ACT Now Policy and Communications Fellow</t>
   </si>
   <si>
@@ -442,9 +481,6 @@
     <t>Cambridge, Massachusetts</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 48000.00 - 56000.00/year</t>
   </si>
   <si>
@@ -454,6 +490,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/388e1835a57947d59fdc73d44c2dd419-administrative-assistant-de-novo-center-for-justice-and-healing-cambridge</t>
   </si>
   <si>
+    <t>Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>North East Community Center (Dutchess County, NY)</t>
+  </si>
+  <si>
+    <t>Millerton, New York</t>
+  </si>
+  <si>
+    <t>USD 28.57 - 31.86/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0820d0689f624dcca71e51a33e5d5ce6-administrative-coordinator-north-east-community-center-dutchess-county-ny-millerton</t>
+  </si>
+  <si>
     <t>Agente en vía pública | CABA y GBA</t>
   </si>
   <si>
@@ -517,15 +571,24 @@
     <t>Associate General Counsel for NYS Attorney General (3922)</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 91506.00 - 190644.00/year</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/government-job/c422276a02c941c89b689b3ce9cea0d0-associate-general-counsel-for-nys-attorney-general-3922-new-york-state-office-of-the-attorney-general-new-york</t>
   </si>
   <si>
+    <t>Associate I, Evidence Project</t>
+  </si>
+  <si>
+    <t>The Pew Charitable Trusts</t>
+  </si>
+  <si>
+    <t>USD 69050.00 - 77170.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c861680dc7a64e8abab8881288c71371-associate-i-evidence-project-the-pew-charitable-trusts-washington</t>
+  </si>
+  <si>
     <t>Attorney: Investigate and Litigate Affirmative Cases (3921)</t>
   </si>
   <si>
@@ -544,6 +607,60 @@
     <t>https://www.idealist.org/en/government-job/af28a898fd4640b5a791929351aa9d05-attorney-transactions-section-charities-bureau-3920-new-york-state-office-of-the-attorney-general-new-york</t>
   </si>
   <si>
+    <t>Behavioral Youth Counselor</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Memphis, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 64000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b8e6057d3c04c0eb93941e7f59006f3-behavioral-youth-counselor-youth-villages-memphis</t>
+  </si>
+  <si>
+    <t>Bilingual Administrative Assistant in Los Angeles</t>
+  </si>
+  <si>
+    <t>Immigration Center for Women and Children</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1274561b838842df838a02fcdfe37b14-bilingual-administrative-assistant-in-los-angeles-immigration-center-for-women-and-children-los-angeles</t>
+  </si>
+  <si>
+    <t>Bilingual Public Benefits Paralegal -- Northeast PA</t>
+  </si>
+  <si>
+    <t>Community Justice Project</t>
+  </si>
+  <si>
+    <t>Scranton, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 18.74/hour</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/48197f16793a427990c17faa32a10ea7-bilingual-public-benefits-paralegal-northeast-pa-community-justice-project-scranton</t>
+  </si>
+  <si>
     <t>Billing Specialist</t>
   </si>
   <si>
@@ -634,6 +751,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/9efaa886932843328e80da8cb15044a7-chief-development-officer-family-promise-summit</t>
   </si>
   <si>
+    <t>Chief Program Officer</t>
+  </si>
+  <si>
+    <t>Bridging Access To Care Inc</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce177b0278da4bceb91d89adf44800c7-chief-program-officer-bridging-access-to-care-inc-kings-county</t>
+  </si>
+  <si>
     <t>Child Welfare Driver</t>
   </si>
   <si>
@@ -643,6 +775,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/0cf644fc24ad4dfe8ddb361e13eb88b2-child-welfare-driver-shelter-home-for-children-petaling-jaya</t>
   </si>
   <si>
+    <t>Childcare Provider</t>
+  </si>
+  <si>
+    <t>First Unitarian Fellowship of Nanaimo</t>
+  </si>
+  <si>
+    <t>Nanaimo, British Columbia, CA</t>
+  </si>
+  <si>
+    <t>CAD 24.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Environment, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f97426bb27a1425cb4bebffe908b754e-childcare-provider-first-unitarian-fellowship-of-nanaimo-nanaimo</t>
+  </si>
+  <si>
+    <t>Client Services and Data Associate</t>
+  </si>
+  <si>
+    <t>The Children's Law Center NY</t>
+  </si>
+  <si>
+    <t>USD 60180.00 - 79067.32/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/616d9bec83e74555a23298344dada2fd-client-services-and-data-associate-the-childrens-law-center-ny-new-york</t>
+  </si>
+  <si>
     <t>College and Career Success, Program Manager (Years 3 &amp; 4)</t>
   </si>
   <si>
@@ -670,6 +835,21 @@
     <t>https://www.idealist.org/en/job/8dca534f618141e2ab822e01ae951f6b-communications-and-outreach-associate-the-choice-inc-washington</t>
   </si>
   <si>
+    <t>Communications Associate</t>
+  </si>
+  <si>
+    <t>Afterschool Alliance</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77d8d7ebc2104efe9d7df480b40d267d-communications-associate-afterschool-alliance-washington</t>
+  </si>
+  <si>
     <t>Community Development Manager</t>
   </si>
   <si>
@@ -703,6 +883,72 @@
     <t>https://www.idealist.org/en/nonprofit-job/0b3bcb84b4c8416085f522b6a2d9feed-community-justice-attorney-immigrant-rights-program-afsc-american-friends-service-committee-newark</t>
   </si>
   <si>
+    <t>Congregational Account Manager and CRM Specialist</t>
+  </si>
+  <si>
+    <t>Congregation Etz Chayim</t>
+  </si>
+  <si>
+    <t>Palo Alto, California</t>
+  </si>
+  <si>
+    <t>USD 38.00 - 42.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e7f3b8e670a64508907d91bb3152b191-congregational-account-manager-and-crm-specialist-congregation-etz-chayim-palo-alto</t>
+  </si>
+  <si>
+    <t>Continuing Education Associate</t>
+  </si>
+  <si>
+    <t>CAI</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f640d9df7e34f7fb2a74efa67729485-continuing-education-associate-cai-new-york</t>
+  </si>
+  <si>
+    <t>Contract Compliance Manager</t>
+  </si>
+  <si>
+    <t>Social and Environmental Entrepreneurs Inc.</t>
+  </si>
+  <si>
+    <t>USD 118000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b41025794ce47c18486ac10801d0eb2-contract-compliance-manager-social-and-environmental-entrepreneurs-inc-calabasas</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Autistry Studios</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63b2f32ab5c44bfd961db5c844cd7aad-controller-autistry-studios-san-rafael</t>
+  </si>
+  <si>
     <t>Coordinator, Strategic Initiatives</t>
   </si>
   <si>
@@ -763,6 +1009,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/8eebdf3866fe416785ce95b7d088e5bb-development-associate-part-time-pet-partners-bellevue-wa-headquarters-in-office-pet-partners-bellevue</t>
   </si>
   <si>
+    <t>Digital Communications Manager</t>
+  </si>
+  <si>
+    <t>Center for US Global Leadership</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Hunger Food Security, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9fe24afa437a44c59cf43993213a4644-digital-communications-manager-center-for-us-global-leadership-washington</t>
+  </si>
+  <si>
     <t>Digital Media and Communications Coordinator</t>
   </si>
   <si>
@@ -781,6 +1042,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/5d5ebd4961bf45d7b80a4fa1e2ea31f5-digital-media-and-communications-coordinator-do-good-institute-college-park</t>
   </si>
   <si>
+    <t>Director - Institutional Development</t>
+  </si>
+  <si>
+    <t>Elevate</t>
+  </si>
+  <si>
+    <t>USD 72500.00 - 72500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/e7ed462ba65b4f5bba75309df0c024ba-director-institutional-development-elevate-washington</t>
+  </si>
+  <si>
     <t>Director of Charitable Planning</t>
   </si>
   <si>
@@ -805,9 +1078,6 @@
     <t>Rockwall, Texas</t>
   </si>
   <si>
-    <t>USD 70000.00 - 80000.00/year</t>
-  </si>
-  <si>
     <t>Veterans</t>
   </si>
   <si>
@@ -1000,9 +1270,6 @@
     <t>BloomAgainBklyn, Inc.</t>
   </si>
   <si>
-    <t>Kings County, New York</t>
-  </si>
-  <si>
     <t>USD 125000.00 - 125000.00/year</t>
   </si>
   <si>
@@ -1027,6 +1294,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/dc36f6f481954c37b7b5a72351430308-executive-director-aurora-east-education-foundation-aurora</t>
   </si>
   <si>
+    <t>Facilitador/a de Conversatorio Virtual (Tematica: Discapacidad, Inclusión y vida cotidiana)</t>
+  </si>
+  <si>
+    <t>MATEADAS INCLUSIVAS</t>
+  </si>
+  <si>
+    <t>Remote (AR)</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a86e7e37da848cf92f1ebf53fad57a4-facilitadora-de-conversatorio-virtual-tematica-discapacidad-inclusion-y-vida-cotidiana-mateadas-inclusivas-buenos-aires</t>
+  </si>
+  <si>
+    <t>Family Service Worker</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d070facefd649aeb905750498ffdc49-family-service-worker-youth-villages-memphis</t>
+  </si>
+  <si>
     <t>USD 90000.00 - 110000.00/year</t>
   </si>
   <si>
@@ -1054,6 +1348,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/f3fb9cea436b40f6819d17d30b3d9990-finance-budget-manager-partners-for-public-good-los-angeles</t>
   </si>
   <si>
+    <t>Finance and Administrative Operations Director</t>
+  </si>
+  <si>
+    <t>North Carolina Association of Educators</t>
+  </si>
+  <si>
+    <t>Raleigh, North Carolina</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/444aed2142634d1cb23887468330df7d-finance-and-administrative-operations-director-north-carolina-association-of-educators-raleigh</t>
+  </si>
+  <si>
     <t>Finance and Operations Manager (Part-Time)</t>
   </si>
   <si>
@@ -1159,6 +1465,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/aa1eed498e414c38a00704c30eb45fa1-head-of-programmes-seed-madagascar-taolagnaro</t>
   </si>
   <si>
+    <t>Independently Licensed Therapist Two Full-Time Openings | $67,000–$80,000 annually</t>
+  </si>
+  <si>
+    <t>Marian House, Inc.</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Women, Family, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd5da390f39244a88d304916c53b367b-independently-licensed-therapist-two-full-time-openings-6700080000-annually-marian-house-inc-baltimore</t>
+  </si>
+  <si>
     <t>Information &amp; Referral Specialist</t>
   </si>
   <si>
@@ -1192,6 +1516,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/66eb6ca5504641d6a410b6a85f912bcf-international-director-2027-swift-sports-organisation-kampala</t>
   </si>
   <si>
+    <t>Laboratory Technologist</t>
+  </si>
+  <si>
+    <t>Civilian Welfare Foundation</t>
+  </si>
+  <si>
+    <t>Bolpur, West Bengal, IN</t>
+  </si>
+  <si>
+    <t>INR 120000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c4fe52905e24ed39bf1bc1839ed3f46-laboratory-technologist-civilian-welfare-foundation-bolpur</t>
+  </si>
+  <si>
     <t>Land Preservation Grants Assistant</t>
   </si>
   <si>
@@ -1222,6 +1561,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/b31f65111d4f44b99b6099d7f5d29263-lead-staff-attorney-medical-financial-legal-partnership-tzedek-dc-washington</t>
   </si>
   <si>
+    <t>Litigation Strategy Director</t>
+  </si>
+  <si>
+    <t>Southern Environmental Law Center</t>
+  </si>
+  <si>
+    <t>Charlottesville, Virginia</t>
+  </si>
+  <si>
+    <t>USD 188200.00 - 202800.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/492df8055c1044c7be66e70531957729-litigation-strategy-director-southern-environmental-law-center-charlottesville</t>
+  </si>
+  <si>
+    <t>Major and Planned Giving Officer</t>
+  </si>
+  <si>
+    <t>EARTHWORKS</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/752c2f5fe39f481c8b4007cce860b823-major-and-planned-giving-officer-earthworks-washington</t>
+  </si>
+  <si>
     <t>Major Donor Associate</t>
   </si>
   <si>
@@ -1255,12 +1627,18 @@
     <t>Manager of Fundraising Events</t>
   </si>
   <si>
-    <t>USD 55000.00 - 65000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/a7b3dae71a85482aad626d5b18fc90d8-manager-of-fundraising-events-parkinsons-foundation-miami</t>
   </si>
   <si>
+    <t>Manager, Development</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 77000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30407348b72c4f569319ef80da586976-manager-development-campus-compact-boston</t>
+  </si>
+  <si>
     <t>Managing Social Worker</t>
   </si>
   <si>
@@ -1342,9 +1720,6 @@
     <t>After-School All-Stars</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 80000.00 - 95000.00/year</t>
   </si>
   <si>
@@ -1363,6 +1738,21 @@
     <t>https://www.idealist.org/en/government-job/d97d1bfd88434ed68921a6881a4260c4-office-of-special-investigation-legal-support-analyst-6467-new-york-state-office-of-the-attorney-general-new-york</t>
   </si>
   <si>
+    <t>Operations and Grants Coordinator</t>
+  </si>
+  <si>
+    <t>Careers In Nonprofits, Inc.</t>
+  </si>
+  <si>
+    <t>Westchester, Illinois</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 61000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/628a1738c93146abbc94f239e6c9a524-operations-and-grants-coordinator-careers-in-nonprofits-inc-westchester</t>
+  </si>
+  <si>
     <t>P/T Preschool Teacher Assistant- East Orange Preschool</t>
   </si>
   <si>
@@ -1402,6 +1792,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/23de5b6cd102403798ac23dc6772d93a-paralegal-detention-removal-defense-legal-services-of-new-jersey-edison</t>
   </si>
   <si>
+    <t>Part Time HR Consultant</t>
+  </si>
+  <si>
+    <t>Santa Monica Mountains Fund</t>
+  </si>
+  <si>
+    <t>Thousand Oaks, California</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af23c08925614e1d83a285052136a539-part-time-hr-consultant-santa-monica-mountains-fund-thousand-oaks</t>
+  </si>
+  <si>
     <t>PERSONAL DE CUIDADO DE ADULTOS MAYORES</t>
   </si>
   <si>
@@ -1429,6 +1834,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/9661263060bd4949b8c7ffbd79ea48d4-political-director-sunrise-movement-philadelphia</t>
   </si>
   <si>
+    <t>Presentación espontánea para empleo en Hogares de Niños</t>
+  </si>
+  <si>
+    <t>Hogar de Niños María Luisa</t>
+  </si>
+  <si>
+    <t>Villa General Juan Gregorio de Las Heras, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Human Rights Civil Liberties, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37fd88feccf24405ae8dd71e9ef1698b-presentacion-espontanea-para-empleo-en-hogares-de-ninos-hogar-de-ninos-maria-luisa-villa-general-juan-gregorio-de-las-heras</t>
+  </si>
+  <si>
     <t>Program Associate, Institutional Grants</t>
   </si>
   <si>
@@ -1501,6 +1921,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/ac902488b5ba4e13bcdeac02da43d3da-programs-specialist-national-hydropower-association-washington</t>
   </si>
   <si>
+    <t>Project Manager (Program Management Department) [based in Seoul]</t>
+  </si>
+  <si>
+    <t>International Vaccine Institute</t>
+  </si>
+  <si>
+    <t>Seoul, Seoul, KR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/39936717e27a4ac28073caa24931ca8d-project-manager-program-management-department-based-in-seoul-international-vaccine-institute-seoul</t>
+  </si>
+  <si>
+    <t>Psychologist and Project Co-ordinator</t>
+  </si>
+  <si>
+    <t>INR 240000.00 - 240000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/906cdb55cbba4124a7ad3a13d1ad5921-psychologist-and-project-co-ordinator-civilian-welfare-foundation-bolpur</t>
+  </si>
+  <si>
     <t>Quality Improvement Manager</t>
   </si>
   <si>
@@ -1510,6 +1951,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/91b54fbdbdb64cf583d2269ce34bd6ee-quality-improvement-manager-springwell-inc-waltham</t>
   </si>
   <si>
+    <t>Real Estate Development Project Manager</t>
+  </si>
+  <si>
+    <t>Jubilee Housing</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ed1c919eba0f4e8691fb52bc5dffc1d1-real-estate-development-project-manager-jubilee-housing-washington</t>
+  </si>
+  <si>
     <t>Receptionist</t>
   </si>
   <si>
@@ -1594,6 +2047,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/58c0bf015dd14a6cabe56545f80bfa3d-senior-counsel-whistleblower-aid-washington</t>
   </si>
   <si>
+    <t>Senior Development Officer</t>
+  </si>
+  <si>
+    <t>Bonefish &amp; Tarpon Trust</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>Environment, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0076fe137d6f4d4ca446fe6bee5fcc07-senior-development-officer-bonefish-tarpon-trust-miami</t>
+  </si>
+  <si>
     <t>Senior Director of Medicaid Policy</t>
   </si>
   <si>
@@ -1726,9 +2194,6 @@
     <t>JobsFirst NEPA</t>
   </si>
   <si>
-    <t>Scranton, Pennsylvania</t>
-  </si>
-  <si>
     <t>USD 70000.00 - 75000.00/year</t>
   </si>
   <si>
@@ -1744,6 +2209,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/bfa60552e0d74c8a86cf3e739ff23735-southeast-region-lands-project-manager-american-battlefield-trust-washington</t>
   </si>
   <si>
+    <t>Specialist, Lifesaving and Care - Dogtown</t>
+  </si>
+  <si>
+    <t>Best Friends Animal Society</t>
+  </si>
+  <si>
+    <t>Kanab, Utah</t>
+  </si>
+  <si>
+    <t>USD 22.50/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d64688f15c854746a5d1175c3e2418ca-specialist-lifesaving-and-care-dogtown-best-friends-animal-society-kanab</t>
+  </si>
+  <si>
+    <t>Spring Legal Intern, Reproductive Freedom Alliance</t>
+  </si>
+  <si>
+    <t>Governors Action Alliance</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Policy, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/046af96a63da42d89374d26d2f8c656f-spring-legal-intern-reproductive-freedom-alliance-governors-action-alliance-washington</t>
+  </si>
+  <si>
+    <t>St. Johns Riverkeeper</t>
+  </si>
+  <si>
+    <t>ST JOHNS RIVERKEEPER INC</t>
+  </si>
+  <si>
+    <t>JACKSONVILLE, Florida</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94ee2e5808a44a9d80c1f3cdcb985c54-st-johns-riverkeeper-st-johns-riverkeeper-inc-jacksonville</t>
+  </si>
+  <si>
     <t>Staff Attorney</t>
   </si>
   <si>
@@ -1771,6 +2284,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/250b3bced20f4a828f04006b70c210fb-staff-attorney-detention-removal-defense-legal-services-of-new-jersey-edison</t>
   </si>
   <si>
+    <t>Storytelling and Communications Manager</t>
+  </si>
+  <si>
+    <t>GASP, Inc.</t>
+  </si>
+  <si>
+    <t>Birmingham, Alabama</t>
+  </si>
+  <si>
+    <t>USD 47500.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30ec01210e664091aa604fd065c0965a-storytelling-and-communications-manager-gasp-inc-birmingham</t>
+  </si>
+  <si>
     <t>Supervising Rackets Investigator</t>
   </si>
   <si>
@@ -1789,6 +2320,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/be48a18ff4e74940a77740794cd91baf-supervisor-springwell-inc-waltham</t>
   </si>
   <si>
+    <t>Trail Crew Lead</t>
+  </si>
+  <si>
+    <t>Sitka Trail Works</t>
+  </si>
+  <si>
+    <t>Sitka, Alaska</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 36.00/hour</t>
+  </si>
+  <si>
+    <t>Sports Recreation, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0aaf0d994ee440c9800bf5b437092213-trail-crew-lead-sitka-trail-works-sitka</t>
+  </si>
+  <si>
+    <t>US &amp; International Policy Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bea1b1fe39454336b46b78305d35ae4a-us-international-policy-coordinator-bonefish-tarpon-trust-miami</t>
+  </si>
+  <si>
     <t>Vice President of Horticulture</t>
   </si>
   <si>
@@ -1838,6 +2393,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/9731a844ea364c96af6aa47c0deb7737-volunteer-recruitment-engagement-manager-ronald-mcdonald-house-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Youth Training Specialist 1</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4156acbbd434a75a6e975fa79dec5dd-youth-training-specialist-1-build-2-lead-federal-way</t>
   </si>
   <si>
     <t>Youth Workforce Manager</t>
@@ -2813,7 +3374,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2878,10 +3439,34 @@
         <v>131</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2890,7 +3475,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2931,2420 +3516,3294 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="F2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="F4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F5" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="F6" t="s">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F7" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C8" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F8" t="s">
         <v>128</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="F10" t="s">
         <v>128</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B11" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E11" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="F11" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="D12" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F12" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B13" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E13" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F13" t="s">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B14" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E14" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F14" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C15" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E15" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F15" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C16" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="D16" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="E16" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F16" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B17" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C17" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="F17" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="C18" t="s">
-        <v>214</v>
+        <v>147</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>223</v>
       </c>
       <c r="E18" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="F18" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C19" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E19" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F19" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C20" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E20" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F20" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C21" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="D21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="F21" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s">
-        <v>177</v>
+        <v>246</v>
       </c>
       <c r="C22" t="s">
-        <v>178</v>
+        <v>247</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E22" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="F22" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>250</v>
+      </c>
+      <c r="B23" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" t="s">
+        <v>235</v>
+      </c>
+      <c r="D23" t="s">
+        <v>223</v>
+      </c>
+      <c r="E23" t="s">
+        <v>251</v>
+      </c>
+      <c r="F23" t="s">
         <v>237</v>
       </c>
-      <c r="B23" t="s">
-        <v>238</v>
-      </c>
-      <c r="C23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D23" t="s">
-        <v>142</v>
-      </c>
-      <c r="E23" t="s">
-        <v>240</v>
-      </c>
-      <c r="F23" t="s">
-        <v>241</v>
-      </c>
       <c r="H23" s="2" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C24" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="D24" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="E24" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="F24" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C25" t="s">
-        <v>251</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E25" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="F25" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="C26" t="s">
-        <v>257</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E26" t="s">
-        <v>258</v>
+        <v>149</v>
       </c>
       <c r="F26" t="s">
-        <v>128</v>
+        <v>237</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C27" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="E27" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F27" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C28" t="s">
-        <v>268</v>
+        <v>180</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E28" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F28" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B29" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C29" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E29" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F29" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C30" t="s">
-        <v>167</v>
+        <v>285</v>
       </c>
       <c r="D30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E30" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="F30" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C31" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D31" t="s">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="E31" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F31" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C32" t="s">
-        <v>134</v>
+        <v>241</v>
       </c>
       <c r="D32" t="s">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="E32" t="s">
-        <v>128</v>
+        <v>297</v>
       </c>
       <c r="F32" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C33" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D33" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="F33" t="s">
-        <v>128</v>
+        <v>303</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="C34" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="D34" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E34" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="F34" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="C35" t="s">
-        <v>302</v>
+        <v>241</v>
       </c>
       <c r="D35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E35" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="F35" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s">
-        <v>305</v>
+        <v>216</v>
       </c>
       <c r="C36" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="D36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E36" t="s">
-        <v>220</v>
+        <v>317</v>
       </c>
       <c r="F36" t="s">
-        <v>306</v>
+        <v>219</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B37" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C37" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E37" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="F37" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="C38" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D38" t="s">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="F38" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C39" t="s">
-        <v>319</v>
+        <v>180</v>
       </c>
       <c r="D39" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E39" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="F39" t="s">
-        <v>198</v>
+        <v>334</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="C40" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="D40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E40" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="F40" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="C41" t="s">
-        <v>328</v>
+        <v>241</v>
       </c>
       <c r="D41" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="F41" t="s">
-        <v>330</v>
+        <v>128</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="C42" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="E42" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="F42" t="s">
-        <v>335</v>
+        <v>128</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>352</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>353</v>
       </c>
       <c r="D43" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" t="s">
         <v>142</v>
       </c>
-      <c r="E43" t="s">
-        <v>337</v>
-      </c>
       <c r="F43" t="s">
-        <v>338</v>
-      </c>
-      <c r="G43" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="B44" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="C44" t="s">
-        <v>202</v>
+        <v>358</v>
       </c>
       <c r="D44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E44" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="F44" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="C45" t="s">
-        <v>162</v>
+        <v>363</v>
       </c>
       <c r="D45" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="E45" t="s">
-        <v>240</v>
+        <v>364</v>
       </c>
       <c r="F45" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B46" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="C46" t="s">
-        <v>352</v>
+        <v>140</v>
       </c>
       <c r="D46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E46" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="F46" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s">
-        <v>153</v>
+        <v>372</v>
       </c>
       <c r="C47" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="D47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E47" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="F47" t="s">
-        <v>128</v>
+        <v>375</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="B48" t="s">
-        <v>153</v>
+        <v>378</v>
       </c>
       <c r="C48" t="s">
-        <v>361</v>
+        <v>147</v>
       </c>
       <c r="D48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E48" t="s">
-        <v>358</v>
+        <v>128</v>
       </c>
       <c r="F48" t="s">
-        <v>128</v>
+        <v>379</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="B49" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C49" t="s">
-        <v>167</v>
+        <v>321</v>
       </c>
       <c r="D49" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E49" t="s">
+        <v>383</v>
+      </c>
+      <c r="F49" t="s">
         <v>128</v>
       </c>
-      <c r="F49" t="s">
-        <v>365</v>
-      </c>
       <c r="H49" s="2" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="C50" t="s">
-        <v>202</v>
+        <v>387</v>
       </c>
       <c r="D50" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E50" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="F50" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="C51" t="s">
-        <v>167</v>
+        <v>392</v>
       </c>
       <c r="D51" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E51" t="s">
-        <v>337</v>
+        <v>388</v>
       </c>
       <c r="F51" t="s">
-        <v>128</v>
+        <v>389</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="B52" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="C52" t="s">
-        <v>377</v>
+        <v>180</v>
       </c>
       <c r="D52" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E52" t="s">
-        <v>378</v>
+        <v>280</v>
       </c>
       <c r="F52" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s">
-        <v>177</v>
+        <v>398</v>
       </c>
       <c r="C53" t="s">
-        <v>178</v>
+        <v>399</v>
       </c>
       <c r="D53" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E53" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="F53" t="s">
-        <v>180</v>
+        <v>401</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>384</v>
+        <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>177</v>
+        <v>403</v>
       </c>
       <c r="C54" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="D54" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E54" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="F54" t="s">
-        <v>180</v>
+        <v>406</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>387</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="C55" t="s">
-        <v>202</v>
+        <v>409</v>
       </c>
       <c r="D55" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E55" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="F55" t="s">
-        <v>390</v>
+        <v>237</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>392</v>
+        <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="C56" t="s">
-        <v>162</v>
+        <v>413</v>
       </c>
       <c r="D56" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E56" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="F56" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>397</v>
+        <v>49</v>
       </c>
       <c r="B57" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="C57" t="s">
-        <v>162</v>
+        <v>247</v>
       </c>
       <c r="D57" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E57" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="F57" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>402</v>
+        <v>49</v>
       </c>
       <c r="B58" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C58" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="D58" t="s">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="E58" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="F58" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="B59" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="C59" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="D59" t="s">
-        <v>142</v>
+        <v>429</v>
       </c>
       <c r="E59" t="s">
-        <v>409</v>
+        <v>128</v>
       </c>
       <c r="F59" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="B60" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="C60" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D60" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E60" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="F60" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>415</v>
+        <v>55</v>
       </c>
       <c r="B61" t="s">
-        <v>416</v>
+        <v>56</v>
       </c>
       <c r="C61" t="s">
-        <v>417</v>
+        <v>57</v>
       </c>
       <c r="D61" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E61" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="F61" t="s">
-        <v>164</v>
+        <v>436</v>
+      </c>
+      <c r="G61" t="s">
+        <v>437</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s">
-        <v>376</v>
+        <v>440</v>
       </c>
       <c r="C62" t="s">
-        <v>377</v>
+        <v>241</v>
       </c>
       <c r="D62" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E62" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="F62" t="s">
-        <v>379</v>
+        <v>442</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="B63" t="s">
+        <v>445</v>
+      </c>
+      <c r="C63" t="s">
+        <v>446</v>
+      </c>
+      <c r="D63" t="s">
+        <v>141</v>
+      </c>
+      <c r="E63" t="s">
+        <v>128</v>
+      </c>
+      <c r="F63" t="s">
         <v>424</v>
       </c>
-      <c r="C63" t="s">
-        <v>425</v>
-      </c>
-      <c r="D63" t="s">
-        <v>142</v>
-      </c>
-      <c r="E63" t="s">
-        <v>426</v>
-      </c>
-      <c r="F63" t="s">
-        <v>427</v>
-      </c>
       <c r="H63" s="2" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="B64" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="C64" t="s">
-        <v>431</v>
+        <v>180</v>
       </c>
       <c r="D64" t="s">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="E64" t="s">
-        <v>432</v>
+        <v>322</v>
       </c>
       <c r="F64" t="s">
-        <v>128</v>
+        <v>450</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="B65" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="C65" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="D65" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E65" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="F65" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="B66" t="s">
-        <v>441</v>
+        <v>171</v>
       </c>
       <c r="C66" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="D66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E66" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="F66" t="s">
-        <v>444</v>
+        <v>128</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="B67" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C67" t="s">
-        <v>167</v>
+        <v>463</v>
       </c>
       <c r="D67" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E67" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="F67" t="s">
         <v>128</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="B68" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="C68" t="s">
-        <v>451</v>
+        <v>140</v>
       </c>
       <c r="D68" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="E68" t="s">
-        <v>452</v>
+        <v>128</v>
       </c>
       <c r="F68" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>470</v>
       </c>
       <c r="C69" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="D69" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E69" t="s">
-        <v>413</v>
+        <v>471</v>
       </c>
       <c r="F69" t="s">
-        <v>164</v>
+        <v>472</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="B70" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="C70" t="s">
-        <v>459</v>
+        <v>140</v>
       </c>
       <c r="D70" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E70" t="s">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="F70" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="B71" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="C71" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="D71" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="E71" t="s">
-        <v>128</v>
+        <v>480</v>
       </c>
       <c r="F71" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="B72" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="C72" t="s">
-        <v>202</v>
+        <v>485</v>
       </c>
       <c r="D72" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E72" t="s">
-        <v>324</v>
+        <v>486</v>
       </c>
       <c r="F72" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="B73" t="s">
-        <v>472</v>
+        <v>216</v>
       </c>
       <c r="C73" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="D73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E73" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="F73" t="s">
-        <v>474</v>
+        <v>219</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="B74" t="s">
-        <v>472</v>
+        <v>216</v>
       </c>
       <c r="C74" t="s">
-        <v>202</v>
+        <v>493</v>
       </c>
       <c r="D74" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E74" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="F74" t="s">
-        <v>478</v>
+        <v>219</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="B75" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
       <c r="C75" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="D75" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="E75" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="F75" t="s">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="B76" t="s">
-        <v>376</v>
+        <v>501</v>
       </c>
       <c r="C76" t="s">
-        <v>377</v>
+        <v>502</v>
       </c>
       <c r="D76" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E76" t="s">
+        <v>503</v>
+      </c>
+      <c r="F76" t="s">
         <v>128</v>
       </c>
-      <c r="F76" t="s">
-        <v>484</v>
-      </c>
       <c r="H76" s="2" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="B77" t="s">
-        <v>376</v>
+        <v>506</v>
       </c>
       <c r="C77" t="s">
-        <v>377</v>
+        <v>180</v>
       </c>
       <c r="D77" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E77" t="s">
-        <v>128</v>
+        <v>507</v>
       </c>
       <c r="F77" t="s">
-        <v>379</v>
+        <v>508</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>487</v>
+        <v>509</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>488</v>
+        <v>510</v>
       </c>
       <c r="B78" t="s">
-        <v>376</v>
+        <v>511</v>
       </c>
       <c r="C78" t="s">
-        <v>377</v>
+        <v>180</v>
       </c>
       <c r="D78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E78" t="s">
-        <v>128</v>
+        <v>512</v>
       </c>
       <c r="F78" t="s">
-        <v>379</v>
+        <v>513</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>489</v>
+        <v>514</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="B79" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="C79" t="s">
-        <v>162</v>
+        <v>517</v>
       </c>
       <c r="D79" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E79" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="F79" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="B80" t="s">
-        <v>177</v>
+        <v>522</v>
       </c>
       <c r="C80" t="s">
-        <v>178</v>
+        <v>241</v>
       </c>
       <c r="D80" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E80" t="s">
-        <v>496</v>
+        <v>523</v>
       </c>
       <c r="F80" t="s">
-        <v>180</v>
+        <v>524</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>497</v>
+        <v>525</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="B81" t="s">
-        <v>499</v>
+        <v>527</v>
       </c>
       <c r="C81" t="s">
-        <v>239</v>
+        <v>528</v>
       </c>
       <c r="D81" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E81" t="s">
-        <v>500</v>
+        <v>529</v>
       </c>
       <c r="F81" t="s">
-        <v>164</v>
+        <v>530</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>501</v>
+        <v>531</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="B82" t="s">
-        <v>177</v>
+        <v>527</v>
       </c>
       <c r="C82" t="s">
-        <v>178</v>
+        <v>528</v>
       </c>
       <c r="D82" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E82" t="s">
-        <v>503</v>
+        <v>533</v>
       </c>
       <c r="F82" t="s">
-        <v>180</v>
+        <v>534</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>504</v>
+        <v>535</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>505</v>
+        <v>536</v>
       </c>
       <c r="B83" t="s">
-        <v>506</v>
+        <v>279</v>
       </c>
       <c r="C83" t="s">
-        <v>507</v>
+        <v>241</v>
       </c>
       <c r="D83" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E83" t="s">
-        <v>508</v>
+        <v>275</v>
       </c>
       <c r="F83" t="s">
-        <v>137</v>
+        <v>281</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>510</v>
+        <v>538</v>
       </c>
       <c r="B84" t="s">
-        <v>511</v>
+        <v>312</v>
       </c>
       <c r="C84" t="s">
-        <v>512</v>
+        <v>241</v>
       </c>
       <c r="D84" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E84" t="s">
-        <v>128</v>
+        <v>539</v>
       </c>
       <c r="F84" t="s">
-        <v>513</v>
+        <v>314</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>514</v>
+        <v>540</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="B85" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="C85" t="s">
-        <v>167</v>
+        <v>543</v>
       </c>
       <c r="D85" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E85" t="s">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="F85" t="s">
-        <v>518</v>
+        <v>182</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="B86" t="s">
-        <v>376</v>
+        <v>478</v>
       </c>
       <c r="C86" t="s">
-        <v>377</v>
+        <v>479</v>
       </c>
       <c r="D86" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E86" t="s">
-        <v>128</v>
+        <v>547</v>
       </c>
       <c r="F86" t="s">
-        <v>521</v>
+        <v>481</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>523</v>
+        <v>549</v>
       </c>
       <c r="B87" t="s">
-        <v>161</v>
+        <v>550</v>
       </c>
       <c r="C87" t="s">
-        <v>162</v>
+        <v>551</v>
       </c>
       <c r="D87" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E87" t="s">
-        <v>524</v>
+        <v>552</v>
       </c>
       <c r="F87" t="s">
-        <v>164</v>
+        <v>553</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="B88" t="s">
-        <v>527</v>
+        <v>556</v>
       </c>
       <c r="C88" t="s">
-        <v>162</v>
+        <v>557</v>
       </c>
       <c r="D88" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E88" t="s">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="F88" t="s">
-        <v>529</v>
+        <v>128</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>530</v>
+        <v>559</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>531</v>
+        <v>560</v>
       </c>
       <c r="B89" t="s">
-        <v>532</v>
+        <v>561</v>
       </c>
       <c r="C89" t="s">
-        <v>202</v>
+        <v>562</v>
       </c>
       <c r="D89" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E89" t="s">
-        <v>533</v>
+        <v>563</v>
       </c>
       <c r="F89" t="s">
-        <v>534</v>
+        <v>564</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>535</v>
+        <v>565</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>536</v>
+        <v>566</v>
       </c>
       <c r="B90" t="s">
-        <v>435</v>
+        <v>567</v>
       </c>
       <c r="C90" t="s">
-        <v>436</v>
+        <v>205</v>
       </c>
       <c r="D90" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E90" t="s">
-        <v>537</v>
+        <v>568</v>
       </c>
       <c r="F90" t="s">
-        <v>438</v>
+        <v>569</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>538</v>
+        <v>570</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>539</v>
+        <v>571</v>
       </c>
       <c r="B91" t="s">
-        <v>540</v>
+        <v>171</v>
       </c>
       <c r="C91" t="s">
-        <v>541</v>
+        <v>140</v>
       </c>
       <c r="D91" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E91" t="s">
-        <v>542</v>
+        <v>572</v>
       </c>
       <c r="F91" t="s">
-        <v>543</v>
+        <v>128</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>544</v>
+        <v>573</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>545</v>
+        <v>574</v>
       </c>
       <c r="B92" t="s">
-        <v>546</v>
+        <v>575</v>
       </c>
       <c r="C92" t="s">
-        <v>547</v>
+        <v>576</v>
       </c>
       <c r="D92" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E92" t="s">
-        <v>548</v>
+        <v>577</v>
       </c>
       <c r="F92" t="s">
-        <v>549</v>
+        <v>128</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>550</v>
+        <v>578</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="B93" t="s">
-        <v>552</v>
+        <v>580</v>
       </c>
       <c r="C93" t="s">
-        <v>167</v>
+        <v>581</v>
       </c>
       <c r="D93" t="s">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="E93" t="s">
-        <v>553</v>
+        <v>582</v>
       </c>
       <c r="F93" t="s">
-        <v>306</v>
+        <v>583</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>555</v>
+        <v>585</v>
       </c>
       <c r="B94" t="s">
-        <v>556</v>
+        <v>179</v>
       </c>
       <c r="C94" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="D94" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="E94" t="s">
-        <v>557</v>
+        <v>275</v>
       </c>
       <c r="F94" t="s">
-        <v>558</v>
+        <v>182</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>559</v>
+        <v>586</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>560</v>
+        <v>587</v>
       </c>
       <c r="B95" t="s">
-        <v>561</v>
+        <v>588</v>
       </c>
       <c r="C95" t="s">
-        <v>562</v>
+        <v>589</v>
       </c>
       <c r="D95" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E95" t="s">
-        <v>563</v>
+        <v>590</v>
       </c>
       <c r="F95" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>564</v>
+        <v>591</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>565</v>
+        <v>592</v>
       </c>
       <c r="B96" t="s">
-        <v>458</v>
+        <v>593</v>
       </c>
       <c r="C96" t="s">
-        <v>459</v>
+        <v>594</v>
       </c>
       <c r="D96" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="E96" t="s">
-        <v>566</v>
+        <v>128</v>
       </c>
       <c r="F96" t="s">
-        <v>164</v>
+        <v>595</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>567</v>
+        <v>596</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>568</v>
+        <v>597</v>
       </c>
       <c r="B97" t="s">
-        <v>569</v>
+        <v>598</v>
       </c>
       <c r="C97" t="s">
-        <v>570</v>
+        <v>599</v>
       </c>
       <c r="D97" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E97" t="s">
-        <v>571</v>
+        <v>128</v>
       </c>
       <c r="F97" t="s">
-        <v>558</v>
+        <v>600</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>572</v>
+        <v>601</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>573</v>
+        <v>602</v>
       </c>
       <c r="B98" t="s">
-        <v>393</v>
+        <v>603</v>
       </c>
       <c r="C98" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="D98" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E98" t="s">
-        <v>574</v>
+        <v>414</v>
       </c>
       <c r="F98" t="s">
-        <v>395</v>
+        <v>604</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>575</v>
+        <v>605</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>576</v>
+        <v>606</v>
       </c>
       <c r="B99" t="s">
-        <v>577</v>
+        <v>607</v>
       </c>
       <c r="C99" t="s">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="D99" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E99" t="s">
-        <v>579</v>
+        <v>128</v>
       </c>
       <c r="F99" t="s">
-        <v>580</v>
+        <v>609</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>581</v>
+        <v>610</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>582</v>
+        <v>611</v>
       </c>
       <c r="B100" t="s">
-        <v>458</v>
+        <v>612</v>
       </c>
       <c r="C100" t="s">
-        <v>459</v>
+        <v>241</v>
       </c>
       <c r="D100" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E100" t="s">
-        <v>583</v>
+        <v>613</v>
       </c>
       <c r="F100" t="s">
-        <v>164</v>
+        <v>614</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>584</v>
+        <v>615</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>585</v>
+        <v>616</v>
       </c>
       <c r="B101" t="s">
-        <v>552</v>
+        <v>612</v>
       </c>
       <c r="C101" t="s">
-        <v>167</v>
+        <v>241</v>
       </c>
       <c r="D101" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E101" t="s">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="F101" t="s">
-        <v>306</v>
+        <v>618</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>587</v>
+        <v>619</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>588</v>
+        <v>620</v>
       </c>
       <c r="B102" t="s">
-        <v>177</v>
+        <v>612</v>
       </c>
       <c r="C102" t="s">
-        <v>178</v>
+        <v>241</v>
       </c>
       <c r="D102" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E102" t="s">
-        <v>589</v>
+        <v>621</v>
       </c>
       <c r="F102" t="s">
-        <v>180</v>
+        <v>614</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>590</v>
+        <v>622</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>591</v>
+        <v>623</v>
       </c>
       <c r="B103" t="s">
-        <v>592</v>
+        <v>478</v>
       </c>
       <c r="C103" t="s">
-        <v>593</v>
+        <v>479</v>
       </c>
       <c r="D103" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E103" t="s">
-        <v>594</v>
+        <v>128</v>
       </c>
       <c r="F103" t="s">
-        <v>128</v>
+        <v>624</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>595</v>
+        <v>625</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>596</v>
+        <v>626</v>
       </c>
       <c r="B104" t="s">
-        <v>597</v>
+        <v>478</v>
       </c>
       <c r="C104" t="s">
-        <v>598</v>
+        <v>479</v>
       </c>
       <c r="D104" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E104" t="s">
-        <v>599</v>
+        <v>128</v>
       </c>
       <c r="F104" t="s">
-        <v>600</v>
+        <v>481</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>601</v>
+        <v>627</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>602</v>
+        <v>628</v>
       </c>
       <c r="B105" t="s">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="C105" t="s">
-        <v>604</v>
+        <v>479</v>
       </c>
       <c r="D105" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E105" t="s">
-        <v>605</v>
+        <v>128</v>
       </c>
       <c r="F105" t="s">
-        <v>606</v>
+        <v>481</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>607</v>
+        <v>629</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>608</v>
+        <v>630</v>
       </c>
       <c r="B106" t="s">
-        <v>540</v>
+        <v>631</v>
       </c>
       <c r="C106" t="s">
-        <v>541</v>
+        <v>180</v>
       </c>
       <c r="D106" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E106" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="F106" t="s">
-        <v>543</v>
+        <v>633</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>610</v>
+        <v>634</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>635</v>
+      </c>
+      <c r="B107" t="s">
+        <v>636</v>
+      </c>
+      <c r="C107" t="s">
+        <v>637</v>
+      </c>
+      <c r="D107" t="s">
+        <v>141</v>
+      </c>
+      <c r="E107" t="s">
+        <v>128</v>
+      </c>
+      <c r="F107" t="s">
+        <v>553</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>639</v>
+      </c>
+      <c r="B108" t="s">
+        <v>501</v>
+      </c>
+      <c r="C108" t="s">
+        <v>502</v>
+      </c>
+      <c r="D108" t="s">
+        <v>141</v>
+      </c>
+      <c r="E108" t="s">
+        <v>640</v>
+      </c>
+      <c r="F108" t="s">
+        <v>128</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>642</v>
+      </c>
+      <c r="B109" t="s">
+        <v>216</v>
+      </c>
+      <c r="C109" t="s">
+        <v>217</v>
+      </c>
+      <c r="D109" t="s">
+        <v>141</v>
+      </c>
+      <c r="E109" t="s">
+        <v>643</v>
+      </c>
+      <c r="F109" t="s">
+        <v>219</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>645</v>
+      </c>
+      <c r="B110" t="s">
+        <v>646</v>
+      </c>
+      <c r="C110" t="s">
+        <v>180</v>
+      </c>
+      <c r="D110" t="s">
+        <v>141</v>
+      </c>
+      <c r="E110" t="s">
+        <v>647</v>
+      </c>
+      <c r="F110" t="s">
+        <v>128</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>649</v>
+      </c>
+      <c r="B111" t="s">
+        <v>650</v>
+      </c>
+      <c r="C111" t="s">
+        <v>321</v>
+      </c>
+      <c r="D111" t="s">
+        <v>141</v>
+      </c>
+      <c r="E111" t="s">
+        <v>651</v>
+      </c>
+      <c r="F111" t="s">
+        <v>182</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>653</v>
+      </c>
+      <c r="B112" t="s">
+        <v>216</v>
+      </c>
+      <c r="C112" t="s">
+        <v>217</v>
+      </c>
+      <c r="D112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E112" t="s">
+        <v>654</v>
+      </c>
+      <c r="F112" t="s">
+        <v>219</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>656</v>
+      </c>
+      <c r="B113" t="s">
+        <v>657</v>
+      </c>
+      <c r="C113" t="s">
+        <v>658</v>
+      </c>
+      <c r="D113" t="s">
+        <v>141</v>
+      </c>
+      <c r="E113" t="s">
+        <v>659</v>
+      </c>
+      <c r="F113" t="s">
+        <v>150</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>661</v>
+      </c>
+      <c r="B114" t="s">
+        <v>662</v>
+      </c>
+      <c r="C114" t="s">
+        <v>663</v>
+      </c>
+      <c r="D114" t="s">
+        <v>148</v>
+      </c>
+      <c r="E114" t="s">
+        <v>128</v>
+      </c>
+      <c r="F114" t="s">
+        <v>664</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>666</v>
+      </c>
+      <c r="B115" t="s">
+        <v>667</v>
+      </c>
+      <c r="C115" t="s">
+        <v>140</v>
+      </c>
+      <c r="D115" t="s">
+        <v>141</v>
+      </c>
+      <c r="E115" t="s">
+        <v>668</v>
+      </c>
+      <c r="F115" t="s">
+        <v>669</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>671</v>
+      </c>
+      <c r="B116" t="s">
+        <v>478</v>
+      </c>
+      <c r="C116" t="s">
+        <v>479</v>
+      </c>
+      <c r="D116" t="s">
+        <v>141</v>
+      </c>
+      <c r="E116" t="s">
+        <v>128</v>
+      </c>
+      <c r="F116" t="s">
+        <v>672</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>674</v>
+      </c>
+      <c r="B117" t="s">
+        <v>179</v>
+      </c>
+      <c r="C117" t="s">
+        <v>180</v>
+      </c>
+      <c r="D117" t="s">
+        <v>141</v>
+      </c>
+      <c r="E117" t="s">
+        <v>675</v>
+      </c>
+      <c r="F117" t="s">
+        <v>182</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>677</v>
+      </c>
+      <c r="B118" t="s">
+        <v>678</v>
+      </c>
+      <c r="C118" t="s">
+        <v>679</v>
+      </c>
+      <c r="D118" t="s">
+        <v>141</v>
+      </c>
+      <c r="E118" t="s">
+        <v>128</v>
+      </c>
+      <c r="F118" t="s">
+        <v>680</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>682</v>
+      </c>
+      <c r="B119" t="s">
+        <v>683</v>
+      </c>
+      <c r="C119" t="s">
+        <v>180</v>
+      </c>
+      <c r="D119" t="s">
+        <v>141</v>
+      </c>
+      <c r="E119" t="s">
+        <v>684</v>
+      </c>
+      <c r="F119" t="s">
+        <v>685</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>687</v>
+      </c>
+      <c r="B120" t="s">
+        <v>688</v>
+      </c>
+      <c r="C120" t="s">
+        <v>241</v>
+      </c>
+      <c r="D120" t="s">
+        <v>141</v>
+      </c>
+      <c r="E120" t="s">
+        <v>689</v>
+      </c>
+      <c r="F120" t="s">
+        <v>690</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>692</v>
+      </c>
+      <c r="B121" t="s">
+        <v>561</v>
+      </c>
+      <c r="C121" t="s">
+        <v>562</v>
+      </c>
+      <c r="D121" t="s">
+        <v>141</v>
+      </c>
+      <c r="E121" t="s">
+        <v>693</v>
+      </c>
+      <c r="F121" t="s">
+        <v>564</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>695</v>
+      </c>
+      <c r="B122" t="s">
+        <v>696</v>
+      </c>
+      <c r="C122" t="s">
+        <v>697</v>
+      </c>
+      <c r="D122" t="s">
+        <v>141</v>
+      </c>
+      <c r="E122" t="s">
+        <v>698</v>
+      </c>
+      <c r="F122" t="s">
+        <v>699</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>701</v>
+      </c>
+      <c r="B123" t="s">
+        <v>702</v>
+      </c>
+      <c r="C123" t="s">
+        <v>703</v>
+      </c>
+      <c r="D123" t="s">
+        <v>141</v>
+      </c>
+      <c r="E123" t="s">
+        <v>704</v>
+      </c>
+      <c r="F123" t="s">
+        <v>705</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>707</v>
+      </c>
+      <c r="B124" t="s">
+        <v>708</v>
+      </c>
+      <c r="C124" t="s">
+        <v>140</v>
+      </c>
+      <c r="D124" t="s">
+        <v>141</v>
+      </c>
+      <c r="E124" t="s">
+        <v>709</v>
+      </c>
+      <c r="F124" t="s">
+        <v>396</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>711</v>
+      </c>
+      <c r="B125" t="s">
+        <v>712</v>
+      </c>
+      <c r="C125" t="s">
+        <v>241</v>
+      </c>
+      <c r="D125" t="s">
+        <v>141</v>
+      </c>
+      <c r="E125" t="s">
+        <v>713</v>
+      </c>
+      <c r="F125" t="s">
+        <v>714</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>716</v>
+      </c>
+      <c r="B126" t="s">
+        <v>717</v>
+      </c>
+      <c r="C126" t="s">
+        <v>718</v>
+      </c>
+      <c r="D126" t="s">
+        <v>141</v>
+      </c>
+      <c r="E126" t="s">
+        <v>719</v>
+      </c>
+      <c r="F126" t="s">
+        <v>128</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>721</v>
+      </c>
+      <c r="B127" t="s">
+        <v>588</v>
+      </c>
+      <c r="C127" t="s">
+        <v>589</v>
+      </c>
+      <c r="D127" t="s">
+        <v>141</v>
+      </c>
+      <c r="E127" t="s">
+        <v>722</v>
+      </c>
+      <c r="F127" t="s">
+        <v>182</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>724</v>
+      </c>
+      <c r="B128" t="s">
+        <v>725</v>
+      </c>
+      <c r="C128" t="s">
+        <v>211</v>
+      </c>
+      <c r="D128" t="s">
+        <v>141</v>
+      </c>
+      <c r="E128" t="s">
+        <v>726</v>
+      </c>
+      <c r="F128" t="s">
+        <v>714</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>728</v>
+      </c>
+      <c r="B129" t="s">
+        <v>506</v>
+      </c>
+      <c r="C129" t="s">
+        <v>241</v>
+      </c>
+      <c r="D129" t="s">
+        <v>141</v>
+      </c>
+      <c r="E129" t="s">
+        <v>729</v>
+      </c>
+      <c r="F129" t="s">
+        <v>508</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>731</v>
+      </c>
+      <c r="B130" t="s">
+        <v>732</v>
+      </c>
+      <c r="C130" t="s">
+        <v>733</v>
+      </c>
+      <c r="D130" t="s">
+        <v>141</v>
+      </c>
+      <c r="E130" t="s">
+        <v>734</v>
+      </c>
+      <c r="F130" t="s">
+        <v>360</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>736</v>
+      </c>
+      <c r="B131" t="s">
+        <v>737</v>
+      </c>
+      <c r="C131" t="s">
+        <v>241</v>
+      </c>
+      <c r="D131" t="s">
+        <v>167</v>
+      </c>
+      <c r="E131" t="s">
+        <v>738</v>
+      </c>
+      <c r="F131" t="s">
+        <v>739</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>741</v>
+      </c>
+      <c r="B132" t="s">
+        <v>742</v>
+      </c>
+      <c r="C132" t="s">
+        <v>743</v>
+      </c>
+      <c r="D132" t="s">
+        <v>141</v>
+      </c>
+      <c r="E132" t="s">
+        <v>744</v>
+      </c>
+      <c r="F132" t="s">
+        <v>745</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>747</v>
+      </c>
+      <c r="B133" t="s">
+        <v>748</v>
+      </c>
+      <c r="C133" t="s">
+        <v>749</v>
+      </c>
+      <c r="D133" t="s">
+        <v>141</v>
+      </c>
+      <c r="E133" t="s">
+        <v>750</v>
+      </c>
+      <c r="F133" t="s">
+        <v>751</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>753</v>
+      </c>
+      <c r="B134" t="s">
+        <v>588</v>
+      </c>
+      <c r="C134" t="s">
+        <v>589</v>
+      </c>
+      <c r="D134" t="s">
+        <v>141</v>
+      </c>
+      <c r="E134" t="s">
+        <v>754</v>
+      </c>
+      <c r="F134" t="s">
+        <v>182</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>756</v>
+      </c>
+      <c r="B135" t="s">
+        <v>757</v>
+      </c>
+      <c r="C135" t="s">
+        <v>758</v>
+      </c>
+      <c r="D135" t="s">
+        <v>141</v>
+      </c>
+      <c r="E135" t="s">
+        <v>759</v>
+      </c>
+      <c r="F135" t="s">
+        <v>760</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>762</v>
+      </c>
+      <c r="B136" t="s">
+        <v>708</v>
+      </c>
+      <c r="C136" t="s">
+        <v>140</v>
+      </c>
+      <c r="D136" t="s">
+        <v>141</v>
+      </c>
+      <c r="E136" t="s">
+        <v>763</v>
+      </c>
+      <c r="F136" t="s">
+        <v>396</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>765</v>
+      </c>
+      <c r="B137" t="s">
+        <v>216</v>
+      </c>
+      <c r="C137" t="s">
+        <v>217</v>
+      </c>
+      <c r="D137" t="s">
+        <v>141</v>
+      </c>
+      <c r="E137" t="s">
+        <v>766</v>
+      </c>
+      <c r="F137" t="s">
+        <v>219</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>768</v>
+      </c>
+      <c r="B138" t="s">
+        <v>769</v>
+      </c>
+      <c r="C138" t="s">
+        <v>770</v>
+      </c>
+      <c r="D138" t="s">
+        <v>148</v>
+      </c>
+      <c r="E138" t="s">
+        <v>771</v>
+      </c>
+      <c r="F138" t="s">
+        <v>772</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>774</v>
+      </c>
+      <c r="B139" t="s">
+        <v>678</v>
+      </c>
+      <c r="C139" t="s">
+        <v>241</v>
+      </c>
+      <c r="D139" t="s">
+        <v>141</v>
+      </c>
+      <c r="E139" t="s">
+        <v>128</v>
+      </c>
+      <c r="F139" t="s">
+        <v>680</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>776</v>
+      </c>
+      <c r="B140" t="s">
+        <v>777</v>
+      </c>
+      <c r="C140" t="s">
+        <v>778</v>
+      </c>
+      <c r="D140" t="s">
+        <v>141</v>
+      </c>
+      <c r="E140" t="s">
+        <v>779</v>
+      </c>
+      <c r="F140" t="s">
+        <v>128</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>781</v>
+      </c>
+      <c r="B141" t="s">
+        <v>782</v>
+      </c>
+      <c r="C141" t="s">
+        <v>783</v>
+      </c>
+      <c r="D141" t="s">
+        <v>141</v>
+      </c>
+      <c r="E141" t="s">
+        <v>784</v>
+      </c>
+      <c r="F141" t="s">
+        <v>785</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>787</v>
+      </c>
+      <c r="B142" t="s">
+        <v>788</v>
+      </c>
+      <c r="C142" t="s">
+        <v>789</v>
+      </c>
+      <c r="D142" t="s">
+        <v>141</v>
+      </c>
+      <c r="E142" t="s">
+        <v>790</v>
+      </c>
+      <c r="F142" t="s">
+        <v>791</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>793</v>
+      </c>
+      <c r="B143" t="s">
+        <v>657</v>
+      </c>
+      <c r="C143" t="s">
+        <v>658</v>
+      </c>
+      <c r="D143" t="s">
+        <v>141</v>
+      </c>
+      <c r="E143" t="s">
+        <v>659</v>
+      </c>
+      <c r="F143" t="s">
+        <v>150</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>795</v>
+      </c>
+      <c r="B144" t="s">
+        <v>696</v>
+      </c>
+      <c r="C144" t="s">
+        <v>697</v>
+      </c>
+      <c r="D144" t="s">
+        <v>141</v>
+      </c>
+      <c r="E144" t="s">
+        <v>796</v>
+      </c>
+      <c r="F144" t="s">
+        <v>699</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>797</v>
       </c>
     </row>
   </sheetData>
@@ -5455,6 +6914,44 @@
     <hyperlink ref="H104" r:id="rId103"/>
     <hyperlink ref="H105" r:id="rId104"/>
     <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
